--- a/0.EJEMPLOS_EXAMPLES/NUM ROMANOS/NUM ROMANOS - DATA BASE FILE.xlsx
+++ b/0.EJEMPLOS_EXAMPLES/NUM ROMANOS/NUM ROMANOS - DATA BASE FILE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28422"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milag\Desktop\FastTest_PlugIn_V78\0.EJEMPLOS_EXAMPLES\NUM ROMANOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AHGM\0. GITHUB\FTP_Privado\0.EJEMPLOS_EXAMPLES\NUM ROMANOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87FBDB9-CCE1-4AF4-8D6E-2F42461EF038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C41D50-B127-4466-B048-519BB7138755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="-93" yWindow="-93" windowWidth="19386" windowHeight="12266" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="-93" yWindow="-93" windowWidth="19386" windowHeight="12986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INICIO" sheetId="6" r:id="rId1"/>
@@ -630,7 +630,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="1019">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="1028">
   <si>
     <t>MILAGROS HUERTA GÓMEZ DE MERODIO</t>
   </si>
@@ -3194,9 +3194,6 @@
 默认情况下，根据您要使用的语言编写相应的数字。 您可以随时更改它。</t>
   </si>
   <si>
-    <t>V - 7.8  - 02/04/2023</t>
-  </si>
-  <si>
     <t>Numeros Romanos</t>
   </si>
   <si>
@@ -3759,6 +3756,66 @@
 1. Selecciona el Número Romano de 9 {1:MC:%100%IX#Muy Bien~%-50%XIV#Debes estudiar más~%-50%XV#Debes estudiar más~%-50%XXXI#Debes estudiar más}&lt;br&gt;&lt;br&gt;
 2. Escribe el Número Romano de 31 {1:SA:%100%XXXI#Muy bien~%50%xxxi#Ten cuidado y escribe en Mayúsculas}&lt;br&gt;&lt;br&gt;
 3. Escribe el número de XV{1:NUMERICAL:%100%15:0#Muy bien~%-50%14:0#Debes estudiar mas}</t>
+  </si>
+  <si>
+    <t>V - 8.3  - 02/01/2025</t>
+  </si>
+  <si>
+    <t>Trabajando con Números Romanos:&lt;br&gt;&lt;br&gt;
+0. Selecciona el Número Romano de 9 {1:MC:%100%IX#Muy Bien~%-50%XIV#Debes estudiar más~%-50%XV#Debes estudiar más~%-50%XXXI#Debes estudiar más}&lt;br&gt;&lt;br&gt;
+1. Escribe el Número Romano de 20 {1:SA:%100%XX#Muy bien~%50%xxxi#Ten cuidado y escribe en Mayúsculas}&lt;br&gt;&lt;br&gt;
+2. Escribe el Número Romano de 18 {1:SA:%100%XVIII#Muy bien~%50%xxxi#Ten cuidado y escribe en Mayúsculas}&lt;br&gt;&lt;br&gt;
+3. Escribe el Número Romano de 31 {1:SA:%100%XXXI#Muy bien~%50%xxxi#Ten cuidado y escribe en Mayúsculas}&lt;br&gt;&lt;br&gt;
+4. Escribe el Número Romano de 1 {1:SA:%100%I#Muy bien~%50%xxxi#Ten cuidado y escribe en Mayúsculas}&lt;br&gt;&lt;br&gt;
+5. Escribe el número de XV{1:NUMERICAL:%100%15:0#Muy bien~%-50%14:0#Debes estudiar mas}</t>
+  </si>
+  <si>
+    <t>Trabajando con Números Romanos:&lt;br&gt;&lt;br&gt;
+1. Selecciona el Número Romano de 9 {1:MC:%100%XXV#Muy Bien~%-50%#Debes estudiar más~%-50%XXVI#Debes estudiar más~%-50%#Debes estudiar más}&lt;br&gt;&lt;br&gt;
+2. Escribe el Número Romano de 30 {1:SA:%100%#Muy bien~%50%#Ten cuidado y escribe en Mayúsculas}&lt;br&gt;&lt;br&gt;
+3. Escribe el número de XXVI{1:NUMERICAL:%100%17:0#Muy bien~%-50%10:0#Debes estudiar mas}</t>
+  </si>
+  <si>
+    <t>Trabajando con Números Romanos:&lt;br&gt;&lt;br&gt;
+1. Selecciona el Número Romano de 10 {1:MC:%100%XXV#Muy Bien~%-50%#Debes estudiar más~%-50%XXVI#Debes estudiar más~%-50%#Debes estudiar más}&lt;br&gt;&lt;br&gt;
+2. Escribe el Número Romano de 34 {1:SA:%100%#Muy bien~%50%#Ten cuidado y escribe en Mayúsculas}&lt;br&gt;&lt;br&gt;
+3. Escribe el número de XXVI{1:NUMERICAL:%100%18:0#Muy bien~%-50%13:0#Debes estudiar mas}</t>
+  </si>
+  <si>
+    <t>Trabajando con Números Romanos:&lt;br&gt;&lt;br&gt;
+1. Selecciona el Número Romano de 9 {1:MC:%100%XXV#Muy Bien~%-50%#Debes estudiar más~%-50%XXVI#Debes estudiar más~%-50%#Debes estudiar más}&lt;br&gt;&lt;br&gt;
+2. Escribe el Número Romano de 31 {1:SA:%100%#Muy bien~%50%#Ten cuidado y escribe en Mayúsculas}&lt;br&gt;&lt;br&gt;
+3. Escribe el número de XXVI{1:NUMERICAL:%100%16:0#Muy bien~%-50%12:0#Debes estudiar mas}</t>
+  </si>
+  <si>
+    <t>Trabajando con Números Romanos:&lt;br&gt;&lt;br&gt;
+1. Selecciona el Número Romano de 8 {1:MC:%100%XXV#Muy Bien~%-50%#Debes estudiar más~%-50%XXVI#Debes estudiar más~%-50%#Debes estudiar más}&lt;br&gt;&lt;br&gt;
+2. Escribe el Número Romano de 31 {1:SA:%100%#Muy bien~%50%#Ten cuidado y escribe en Mayúsculas}&lt;br&gt;&lt;br&gt;
+3. Escribe el número de XXVI{1:NUMERICAL:%100%16:0#Muy bien~%-50%10:0#Debes estudiar mas}</t>
+  </si>
+  <si>
+    <t>Trabajando con Números Romanos:&lt;br&gt;&lt;br&gt;
+1. Selecciona el Número Romano de 10 {1:MC:%100%XXV#Muy Bien~%-50%#Debes estudiar más~%-50%XXVI#Debes estudiar más~%-50%#Debes estudiar más}&lt;br&gt;&lt;br&gt;
+2. Escribe el Número Romano de 35 {1:SA:%100%#Muy bien~%50%#Ten cuidado y escribe en Mayúsculas}&lt;br&gt;&lt;br&gt;
+3. Escribe el número de XXVI{1:NUMERICAL:%100%19:0#Muy bien~%-50%13:0#Debes estudiar mas}</t>
+  </si>
+  <si>
+    <t>Trabajando con Números Romanos:&lt;br&gt;&lt;br&gt;
+1. Selecciona el Número Romano de 2 {1:MC:%100%XXV#Muy Bien~%-50%#Debes estudiar más~%-50%XXVI#Debes estudiar más~%-50%#Debes estudiar más}&lt;br&gt;&lt;br&gt;
+2. Escribe el Número Romano de 22 {1:SA:%100%#Muy bien~%50%#Ten cuidado y escribe en Mayúsculas}&lt;br&gt;&lt;br&gt;
+3. Escribe el número de XXVI{1:NUMERICAL:%100%12:0#Muy bien~%-50%3:0#Debes estudiar mas}</t>
+  </si>
+  <si>
+    <t>Trabajando con Números Romanos:&lt;br&gt;&lt;br&gt;
+1. Selecciona el Número Romano de 8 {1:MC:%100%XXV#Muy Bien~%-50%#Debes estudiar más~%-50%XXVI#Debes estudiar más~%-50%#Debes estudiar más}&lt;br&gt;&lt;br&gt;
+2. Escribe el Número Romano de 32 {1:SA:%100%#Muy bien~%50%#Ten cuidado y escribe en Mayúsculas}&lt;br&gt;&lt;br&gt;
+3. Escribe el número de XXVI{1:NUMERICAL:%100%17:0#Muy bien~%-50%10:0#Debes estudiar mas}</t>
+  </si>
+  <si>
+    <t>Trabajando con Números Romanos:&lt;br&gt;&lt;br&gt;
+1. Selecciona el Número Romano de 5 {1:MC:%100%XXV#Muy Bien~%-50%#Debes estudiar más~%-50%XXVI#Debes estudiar más~%-50%#Debes estudiar más}&lt;br&gt;&lt;br&gt;
+2. Escribe el Número Romano de 28 {1:SA:%100%#Muy bien~%50%#Ten cuidado y escribe en Mayúsculas}&lt;br&gt;&lt;br&gt;
+3. Escribe el número de XXVI{1:NUMERICAL:%100%13:0#Muy bien~%-50%7:0#Debes estudiar mas}</t>
   </si>
 </sst>
 </file>
@@ -4617,7 +4674,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="277">
+  <cellXfs count="278">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5388,59 +5445,9 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5464,6 +5471,9 @@
     <xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5479,10 +5489,61 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5494,6 +5555,75 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="348">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE87B00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -6532,36 +6662,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -7283,31 +7383,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE87B00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
@@ -8345,20 +8420,6 @@
         <patternFill>
           <fgColor indexed="64"/>
           <bgColor rgb="FF005877"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -21114,54 +21175,54 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabla_Menu" displayName="Tabla_Menu" ref="S2:AF30" totalsRowCount="1" headerRowDxfId="40" dataDxfId="39" tableBorderDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabla_Menu" displayName="Tabla_Menu" ref="S2:AF30" totalsRowCount="1" headerRowDxfId="46" dataDxfId="45" tableBorderDxfId="44">
   <autoFilter ref="S2:AF29" xr:uid="{00000000-0009-0000-0100-00000C000000}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="N Sub" totalsRowFunction="custom" dataDxfId="37" totalsRowDxfId="36">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="N Sub" totalsRowFunction="custom" dataDxfId="43" totalsRowDxfId="42">
       <calculatedColumnFormula>IF(Tabla_Menu[[#This Row],[Nivel]]=T2,0,COUNTIF(Tabla_Menu[Nivel],Tabla_Menu[[#This Row],[Nivel]]))</calculatedColumnFormula>
       <totalsRowFormula>COUNTIF(Tabla_Menu[N Sub],"&lt;&gt;0")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Nivel" dataDxfId="35" totalsRowDxfId="34">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Nivel" dataDxfId="41" totalsRowDxfId="40">
       <calculatedColumnFormula>IFERROR(INDIRECT(Tabla_Menu[[#This Row],[Nivel 1]]&amp;IDIOMA),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Nombre" dataDxfId="33" totalsRowDxfId="32">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Nombre" dataDxfId="39" totalsRowDxfId="38">
       <calculatedColumnFormula>IFERROR(INDIRECT(Tabla_Menu[[#This Row],[Nivel 2]]&amp;IDIOMA)&amp;IF(Tabla_Menu[[#This Row],[Nivel]]="",""," "&amp;Tabla_Menu[[#This Row],['[Teclas']]]),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="On Action" dataDxfId="31" totalsRowDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="Face Id" dataDxfId="29" totalsRowDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="Begin Group" dataDxfId="27" totalsRowDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="Nivel 1" dataDxfId="25" totalsRowDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="Nivel 2" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0900-00000B000000}" name="Teclas" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0900-00000F000000}" name="HOJAS NO MUESTRA" dataDxfId="19" totalsRowDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0900-00000A000000}" name="N/A" dataDxfId="17" totalsRowDxfId="16">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="On Action" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="Face Id" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="Begin Group" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="Nivel 1" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="Nivel 2" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0900-00000B000000}" name="Teclas" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0900-00000F000000}" name="HOJAS NO MUESTRA" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0900-00000A000000}" name="N/A" dataDxfId="23" totalsRowDxfId="22">
       <calculatedColumnFormula>IF(OR(Tabla_Menu[[#This Row],[Nivel]]="",IFERROR(SEARCH(MID(CELL("nombrearchivo"),FIND(".xlsm]",CELL("nombrearchivo"),1)+6,100),Tabla_Menu[[#This Row],[HOJAS NO MUESTRA]],1),0)&gt;0),"N/A","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0900-00000E000000}" name="Num N/A" dataDxfId="15" totalsRowDxfId="14">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0900-00000E000000}" name="Num N/A" dataDxfId="21" totalsRowDxfId="20">
       <calculatedColumnFormula>IF(Tabla_Menu[[#This Row],[N/A]]="",,COUNTIF(Tabla_Menu[Nivel &amp; Incluir],Tabla_Menu[[#This Row],[Nivel &amp; Incluir]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0900-00000C000000}" name="Nivel &amp; Incluir" dataDxfId="13" totalsRowDxfId="12">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0900-00000C000000}" name="Nivel &amp; Incluir" dataDxfId="19" totalsRowDxfId="18">
       <calculatedColumnFormula>Tabla_Menu[[#This Row],[Nivel]]&amp;Tabla_Menu[[#This Row],[N/A]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0900-000009000000}" name="[Teclas]" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0900-000009000000}" name="[Teclas]" dataDxfId="17" totalsRowDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="Tabla_UCA" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="Tabla_Comandos" displayName="Tabla_Comandos" ref="U37:W44" totalsRowCount="1" headerRowDxfId="9" dataDxfId="8" totalsRowDxfId="6" tableBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="Tabla_Comandos" displayName="Tabla_Comandos" ref="U37:W44" totalsRowCount="1" headerRowDxfId="15" dataDxfId="14" totalsRowDxfId="12" tableBorderDxfId="13">
   <autoFilter ref="U37:W43" xr:uid="{00000000-0009-0000-0100-00000A000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="CommandBars" totalsRowFunction="custom" dataDxfId="5" totalsRowDxfId="4">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="CommandBars" totalsRowFunction="custom" dataDxfId="11" totalsRowDxfId="10">
       <totalsRowFormula>COUNTA(Tabla_Comandos[CommandBars])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="Cambio" dataDxfId="3" totalsRowDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="Activa/Des" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="Cambio" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="Activa/Des" dataDxfId="7" totalsRowDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21447,88 +21508,88 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Tabla_EN" displayName="Tabla_EN" ref="A4:AI14" totalsRowShown="0" headerRowDxfId="117" dataDxfId="116">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Tabla_EN" displayName="Tabla_EN" ref="A4:AI14" totalsRowShown="0" headerRowDxfId="119" dataDxfId="118">
   <autoFilter ref="A4:AI14" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="35">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="C1" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="C2" dataDxfId="114"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Columna1" dataDxfId="113"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Columna2" dataDxfId="112"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="Descripción" dataDxfId="111"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="FastTest PlugIn - ENSAYO_x000a__x000a_Enunciado de la pregunta" dataDxfId="110"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="Formato de la Respuesta_x000a_Requerir texto" dataDxfId="109"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="Requerir texto" dataDxfId="108"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="Tamaño de la caja de entrada" dataDxfId="107"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="Permitir archivos adjuntos" dataDxfId="106"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0700-00000B000000}" name="Archivos adjuntos requeridos" dataDxfId="105"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0700-00000C000000}" name="Plantilla de Respuesta" dataDxfId="104"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0700-00000D000000}" name="Información para el evaluador" dataDxfId="103"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0700-00000E000000}" name="Columna3" dataDxfId="102"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0700-00000F000000}" name="Columna4" dataDxfId="101"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0700-000010000000}" name="Columna5" dataDxfId="100"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0700-000011000000}" name="Columna6" dataDxfId="99"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0700-000012000000}" name="Columna7" dataDxfId="98"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0700-000013000000}" name="Columna8" dataDxfId="97"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0700-000014000000}" name="Columna9" dataDxfId="96"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0700-000015000000}" name="Columna10" dataDxfId="95"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0700-000016000000}" name="Columna11" dataDxfId="94"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0700-000017000000}" name="Columna12" dataDxfId="93"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0700-000018000000}" name="Columna13" dataDxfId="92"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0700-000019000000}" name="Columna14" dataDxfId="91"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0700-00001A000000}" name="Columna15" dataDxfId="90"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0700-00001B000000}" name="Columna16" dataDxfId="89"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0700-00001C000000}" name="Columna17" dataDxfId="88"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0700-00001D000000}" name="Columna18" dataDxfId="87"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0700-00001E000000}" name="Columna19" dataDxfId="86"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0700-00001F000000}" name="Columna20" dataDxfId="85"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0700-000020000000}" name="Columna21" dataDxfId="84"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0700-000021000000}" name="Columna22" dataDxfId="83"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0700-000022000000}" name="Columna23" dataDxfId="82"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0700-000023000000}" name="Imagen" dataDxfId="81"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="C1" dataDxfId="117"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="C2" dataDxfId="116"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Columna1" dataDxfId="115"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Columna2" dataDxfId="114"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="Descripción" dataDxfId="113"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="FastTest PlugIn - ENSAYO_x000a__x000a_Enunciado de la pregunta" dataDxfId="112"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="Formato de la Respuesta_x000a_Requerir texto" dataDxfId="111"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="Requerir texto" dataDxfId="110"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="Tamaño de la caja de entrada" dataDxfId="109"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="Permitir archivos adjuntos" dataDxfId="108"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0700-00000B000000}" name="Archivos adjuntos requeridos" dataDxfId="107"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0700-00000C000000}" name="Plantilla de Respuesta" dataDxfId="106"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0700-00000D000000}" name="Información para el evaluador" dataDxfId="105"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0700-00000E000000}" name="Columna3" dataDxfId="104"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0700-00000F000000}" name="Columna4" dataDxfId="103"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0700-000010000000}" name="Columna5" dataDxfId="102"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0700-000011000000}" name="Columna6" dataDxfId="101"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0700-000012000000}" name="Columna7" dataDxfId="100"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0700-000013000000}" name="Columna8" dataDxfId="99"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0700-000014000000}" name="Columna9" dataDxfId="98"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0700-000015000000}" name="Columna10" dataDxfId="97"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0700-000016000000}" name="Columna11" dataDxfId="96"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0700-000017000000}" name="Columna12" dataDxfId="95"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0700-000018000000}" name="Columna13" dataDxfId="94"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0700-000019000000}" name="Columna14" dataDxfId="93"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0700-00001A000000}" name="Columna15" dataDxfId="92"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0700-00001B000000}" name="Columna16" dataDxfId="91"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0700-00001C000000}" name="Columna17" dataDxfId="90"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0700-00001D000000}" name="Columna18" dataDxfId="89"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0700-00001E000000}" name="Columna19" dataDxfId="88"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0700-00001F000000}" name="Columna20" dataDxfId="87"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0700-000020000000}" name="Columna21" dataDxfId="86"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0700-000021000000}" name="Columna22" dataDxfId="85"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0700-000022000000}" name="Columna23" dataDxfId="84"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0700-000023000000}" name="Imagen" dataDxfId="83"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabla_CL" displayName="Tabla_CL" ref="A4:AI14" totalsRowShown="0" headerRowDxfId="80" dataDxfId="79">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabla_CL" displayName="Tabla_CL" ref="A4:AI14" totalsRowShown="0" headerRowDxfId="82" dataDxfId="81">
   <autoFilter ref="A4:AI14" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
   <tableColumns count="35">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="C1" dataDxfId="78"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="C2" dataDxfId="77"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Columna1" dataDxfId="76"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Columna2" dataDxfId="75"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="Descripcion" dataDxfId="74"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="Enunciado" dataDxfId="73"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="Ancho RC" dataDxfId="72"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="Columna3" dataDxfId="71"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="Ancho IM" dataDxfId="70"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0800-00000A000000}" name="Columna5" dataDxfId="69"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0800-00000B000000}" name="Columna6" dataDxfId="68"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0800-00000C000000}" name="Columna7" dataDxfId="67"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0800-00000D000000}" name="Columna8" dataDxfId="66"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0800-00000E000000}" name="Columna9" dataDxfId="65"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0800-00000F000000}" name="Columna10" dataDxfId="64"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0800-000010000000}" name="Columna11" dataDxfId="63"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0800-000011000000}" name="Columna12" dataDxfId="62"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0800-000012000000}" name="Columna13" dataDxfId="61"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0800-000013000000}" name="Columna14" dataDxfId="60"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0800-000014000000}" name="Columna15" dataDxfId="59"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0800-000015000000}" name="Columna16" dataDxfId="58"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0800-000016000000}" name="Columna17" dataDxfId="57"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0800-000017000000}" name="Columna18" dataDxfId="56"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0800-000018000000}" name="Columna19" dataDxfId="55"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0800-000019000000}" name="Columna20" dataDxfId="54"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0800-00001A000000}" name="Columna21" dataDxfId="53"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0800-00001B000000}" name="Columna22" dataDxfId="52"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0800-00001C000000}" name="Columna23" dataDxfId="51"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0800-00001D000000}" name="Columna24" dataDxfId="50"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0800-00001E000000}" name="Columna25" dataDxfId="49"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0800-00001F000000}" name="Pista 1" dataDxfId="48"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0800-000020000000}" name="Pista 2" dataDxfId="47"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0800-000021000000}" name="Pista 3" dataDxfId="46"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0800-000022000000}" name="Pista 4" dataDxfId="45"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0800-000023000000}" name="Imagen" dataDxfId="44"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="C1" dataDxfId="80"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="C2" dataDxfId="79"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Columna1" dataDxfId="78"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Columna2" dataDxfId="77"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="Descripcion" dataDxfId="76"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="Enunciado" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="Ancho RC" dataDxfId="75"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="Columna3" dataDxfId="74"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="Ancho IM" dataDxfId="73"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0800-00000A000000}" name="Columna5" dataDxfId="72"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0800-00000B000000}" name="Columna6" dataDxfId="71"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0800-00000C000000}" name="Columna7" dataDxfId="70"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0800-00000D000000}" name="Columna8" dataDxfId="69"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0800-00000E000000}" name="Columna9" dataDxfId="68"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0800-00000F000000}" name="Columna10" dataDxfId="67"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0800-000010000000}" name="Columna11" dataDxfId="66"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0800-000011000000}" name="Columna12" dataDxfId="65"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0800-000012000000}" name="Columna13" dataDxfId="64"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0800-000013000000}" name="Columna14" dataDxfId="63"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0800-000014000000}" name="Columna15" dataDxfId="62"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0800-000015000000}" name="Columna16" dataDxfId="61"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0800-000016000000}" name="Columna17" dataDxfId="60"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0800-000017000000}" name="Columna18" dataDxfId="59"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0800-000018000000}" name="Columna19" dataDxfId="58"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0800-000019000000}" name="Columna20" dataDxfId="57"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0800-00001A000000}" name="Columna21" dataDxfId="56"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0800-00001B000000}" name="Columna22" dataDxfId="55"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0800-00001C000000}" name="Columna23" dataDxfId="54"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0800-00001D000000}" name="Columna24" dataDxfId="53"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0800-00001E000000}" name="Columna25" dataDxfId="52"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0800-00001F000000}" name="Pista 1" dataDxfId="51"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0800-000020000000}" name="Pista 2" dataDxfId="50"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0800-000021000000}" name="Pista 3" dataDxfId="49"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0800-000022000000}" name="Pista 4" dataDxfId="48"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0800-000023000000}" name="Imagen" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21809,32 +21870,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="28.7" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="262" t="s">
+      <c r="A1" s="245" t="s">
         <v>387</v>
       </c>
-      <c r="B1" s="252" t="s">
+      <c r="B1" s="264" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="253"/>
-      <c r="D1" s="253"/>
-      <c r="E1" s="253"/>
-      <c r="F1" s="253"/>
-      <c r="G1" s="253"/>
-      <c r="H1" s="253"/>
-      <c r="I1" s="253"/>
-      <c r="J1" s="253"/>
-      <c r="K1" s="253"/>
-      <c r="L1" s="253"/>
-      <c r="M1" s="253"/>
-      <c r="N1" s="253"/>
-      <c r="O1" s="253"/>
-      <c r="P1" s="253"/>
-      <c r="Q1" s="253"/>
-      <c r="R1" s="253"/>
-      <c r="S1" s="254"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
+      <c r="J1" s="265"/>
+      <c r="K1" s="265"/>
+      <c r="L1" s="265"/>
+      <c r="M1" s="265"/>
+      <c r="N1" s="265"/>
+      <c r="O1" s="265"/>
+      <c r="P1" s="265"/>
+      <c r="Q1" s="265"/>
+      <c r="R1" s="265"/>
+      <c r="S1" s="266"/>
     </row>
     <row r="2" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="263"/>
+      <c r="A2" s="246"/>
       <c r="B2" s="4"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -21855,23 +21916,23 @@
       <c r="S2" s="6"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A3" s="263"/>
+      <c r="A3" s="246"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
-      <c r="G3" s="269" t="str">
+      <c r="G3" s="253" t="str">
         <f ca="1">INDIRECT("Z_IN_04_"&amp;IDIOMA)</f>
         <v>Esta Aplicación ha sido desarrollada, en la primera versión, por:</v>
       </c>
-      <c r="H3" s="269"/>
-      <c r="I3" s="269"/>
-      <c r="J3" s="269"/>
-      <c r="K3" s="269"/>
-      <c r="L3" s="269"/>
-      <c r="M3" s="269"/>
-      <c r="N3" s="269"/>
+      <c r="H3" s="253"/>
+      <c r="I3" s="253"/>
+      <c r="J3" s="253"/>
+      <c r="K3" s="253"/>
+      <c r="L3" s="253"/>
+      <c r="M3" s="253"/>
+      <c r="N3" s="253"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
@@ -21879,7 +21940,7 @@
       <c r="S3" s="6"/>
     </row>
     <row r="4" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="263"/>
+      <c r="A4" s="246"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -21900,125 +21961,125 @@
       <c r="S4" s="6"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="263"/>
+      <c r="A5" s="246"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
+      <c r="F5" s="270"/>
+      <c r="G5" s="270"/>
       <c r="H5" s="134"/>
-      <c r="I5" s="270" t="s">
+      <c r="I5" s="254" t="s">
         <v>0</v>
       </c>
-      <c r="J5" s="270"/>
-      <c r="K5" s="270"/>
-      <c r="L5" s="270"/>
+      <c r="J5" s="254"/>
+      <c r="K5" s="254"/>
+      <c r="L5" s="254"/>
       <c r="M5" s="5"/>
-      <c r="N5" s="244"/>
-      <c r="O5" s="244"/>
-      <c r="P5" s="261" t="s">
+      <c r="N5" s="252"/>
+      <c r="O5" s="252"/>
+      <c r="P5" s="271" t="s">
         <v>651</v>
       </c>
-      <c r="Q5" s="261"/>
-      <c r="R5" s="261"/>
+      <c r="Q5" s="271"/>
+      <c r="R5" s="271"/>
       <c r="S5" s="6"/>
     </row>
     <row r="6" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="263"/>
+      <c r="A6" s="246"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="260"/>
-      <c r="G6" s="260"/>
+      <c r="F6" s="270"/>
+      <c r="G6" s="270"/>
       <c r="H6" s="134"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
-      <c r="N6" s="244"/>
-      <c r="O6" s="244"/>
-      <c r="P6" s="272" t="str">
+      <c r="N6" s="252"/>
+      <c r="O6" s="252"/>
+      <c r="P6" s="256" t="str">
         <f ca="1">INDIRECT("Z_IN_01_"&amp;IDIOMA)</f>
         <v>CANAL YOUTUBE</v>
       </c>
-      <c r="Q6" s="272"/>
-      <c r="R6" s="272"/>
+      <c r="Q6" s="256"/>
+      <c r="R6" s="256"/>
       <c r="S6" s="6"/>
     </row>
     <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="263"/>
+      <c r="A7" s="246"/>
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="260"/>
-      <c r="G7" s="260"/>
+      <c r="F7" s="270"/>
+      <c r="G7" s="270"/>
       <c r="H7" s="134"/>
-      <c r="I7" s="269" t="str">
+      <c r="I7" s="253" t="str">
         <f ca="1">INDIRECT("Z_IN_05_"&amp;IDIOMA)</f>
         <v>Universidad de Cádiz</v>
       </c>
-      <c r="J7" s="269"/>
-      <c r="K7" s="269"/>
-      <c r="L7" s="269"/>
+      <c r="J7" s="253"/>
+      <c r="K7" s="253"/>
+      <c r="L7" s="253"/>
       <c r="M7" s="5"/>
-      <c r="N7" s="244"/>
-      <c r="O7" s="244"/>
-      <c r="P7" s="272"/>
-      <c r="Q7" s="272"/>
-      <c r="R7" s="272"/>
+      <c r="N7" s="252"/>
+      <c r="O7" s="252"/>
+      <c r="P7" s="256"/>
+      <c r="Q7" s="256"/>
+      <c r="R7" s="256"/>
       <c r="S7" s="6"/>
     </row>
     <row r="8" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="263"/>
+      <c r="A8" s="246"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="260"/>
-      <c r="G8" s="260"/>
+      <c r="F8" s="270"/>
+      <c r="G8" s="270"/>
       <c r="H8" s="134"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
-      <c r="N8" s="244"/>
-      <c r="O8" s="244"/>
+      <c r="N8" s="252"/>
+      <c r="O8" s="252"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="6"/>
     </row>
     <row r="9" spans="1:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="264"/>
+      <c r="A9" s="247"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="255" t="str">
+      <c r="C9" s="267" t="str">
         <f ca="1">INDIRECT("Z_IN_03_"&amp;IDIOMA)</f>
         <v>LEER CON ATENCIÓN</v>
       </c>
-      <c r="D9" s="255"/>
+      <c r="D9" s="267"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="260"/>
-      <c r="G9" s="260"/>
+      <c r="F9" s="270"/>
+      <c r="G9" s="270"/>
       <c r="H9" s="134"/>
-      <c r="I9" s="271" t="s">
+      <c r="I9" s="255" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="271"/>
-      <c r="K9" s="271"/>
-      <c r="L9" s="271"/>
+      <c r="J9" s="255"/>
+      <c r="K9" s="255"/>
+      <c r="L9" s="255"/>
       <c r="M9" s="5"/>
-      <c r="N9" s="244"/>
-      <c r="O9" s="244"/>
-      <c r="P9" s="273" t="s">
-        <v>831</v>
-      </c>
-      <c r="Q9" s="273"/>
-      <c r="R9" s="273"/>
+      <c r="N9" s="252"/>
+      <c r="O9" s="252"/>
+      <c r="P9" s="257" t="s">
+        <v>1018</v>
+      </c>
+      <c r="Q9" s="257"/>
+      <c r="R9" s="257"/>
       <c r="S9" s="6"/>
     </row>
     <row r="10" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
@@ -22026,256 +22087,256 @@
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="260"/>
-      <c r="G10" s="260"/>
+      <c r="F10" s="270"/>
+      <c r="G10" s="270"/>
       <c r="H10" s="134"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="244"/>
-      <c r="O10" s="244"/>
+      <c r="N10" s="252"/>
+      <c r="O10" s="252"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
       <c r="S10" s="6"/>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="265" t="s">
+      <c r="A11" s="248" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
-      <c r="D11" s="256" t="str">
+      <c r="D11" s="268" t="str">
         <f ca="1">INDIRECT("Z_IN_06_"&amp;IDIOMA)</f>
         <v>1. Esta aplicación se ha desarrollado gracias a un Proyecto de Innovación Docente aprobado por la Unidad de Innovación Docente de la Universidad de Cádiz.
 2. El usuario final es aquel docente que quiera usar los CUESTIONARIOS de la plataforma Moodle. También la puede usar quien quiera tener sus Bancos de Preguntas almacenados en un mismo sitio y con orden.
 3. La aplicación sirve para facilitar la creación de un BANCO DE PREGUNTAS para los cuestionarios, el usuario final deberá repasar que las preguntas se importan bien (al menos las primeras veces) así como si ha rellenado los datos de manera adecuada, como si lo estuviera haciendo en Moodle.
 Pulsa sobre el TIPO DE PREGUNTA sobre el que quieres CONSULTAR las preguntas almacenadas.</v>
       </c>
-      <c r="E11" s="256"/>
-      <c r="F11" s="256"/>
-      <c r="G11" s="256"/>
-      <c r="H11" s="256"/>
-      <c r="I11" s="256"/>
-      <c r="J11" s="256"/>
-      <c r="K11" s="256"/>
-      <c r="L11" s="256"/>
-      <c r="M11" s="256"/>
-      <c r="N11" s="256"/>
-      <c r="O11" s="256"/>
-      <c r="P11" s="256"/>
-      <c r="Q11" s="256"/>
-      <c r="R11" s="256"/>
+      <c r="E11" s="268"/>
+      <c r="F11" s="268"/>
+      <c r="G11" s="268"/>
+      <c r="H11" s="268"/>
+      <c r="I11" s="268"/>
+      <c r="J11" s="268"/>
+      <c r="K11" s="268"/>
+      <c r="L11" s="268"/>
+      <c r="M11" s="268"/>
+      <c r="N11" s="268"/>
+      <c r="O11" s="268"/>
+      <c r="P11" s="268"/>
+      <c r="Q11" s="268"/>
+      <c r="R11" s="268"/>
       <c r="S11" s="6"/>
     </row>
     <row r="12" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="265"/>
+      <c r="A12" s="248"/>
       <c r="B12" s="4"/>
       <c r="C12" s="5"/>
-      <c r="D12" s="256"/>
-      <c r="E12" s="256"/>
-      <c r="F12" s="256"/>
-      <c r="G12" s="256"/>
-      <c r="H12" s="256"/>
-      <c r="I12" s="256"/>
-      <c r="J12" s="256"/>
-      <c r="K12" s="256"/>
-      <c r="L12" s="256"/>
-      <c r="M12" s="256"/>
-      <c r="N12" s="256"/>
-      <c r="O12" s="256"/>
-      <c r="P12" s="256"/>
-      <c r="Q12" s="256"/>
-      <c r="R12" s="256"/>
+      <c r="D12" s="268"/>
+      <c r="E12" s="268"/>
+      <c r="F12" s="268"/>
+      <c r="G12" s="268"/>
+      <c r="H12" s="268"/>
+      <c r="I12" s="268"/>
+      <c r="J12" s="268"/>
+      <c r="K12" s="268"/>
+      <c r="L12" s="268"/>
+      <c r="M12" s="268"/>
+      <c r="N12" s="268"/>
+      <c r="O12" s="268"/>
+      <c r="P12" s="268"/>
+      <c r="Q12" s="268"/>
+      <c r="R12" s="268"/>
       <c r="S12" s="6"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A13" s="265"/>
+      <c r="A13" s="248"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
-      <c r="D13" s="256"/>
-      <c r="E13" s="256"/>
-      <c r="F13" s="256"/>
-      <c r="G13" s="256"/>
-      <c r="H13" s="256"/>
-      <c r="I13" s="256"/>
-      <c r="J13" s="256"/>
-      <c r="K13" s="256"/>
-      <c r="L13" s="256"/>
-      <c r="M13" s="256"/>
-      <c r="N13" s="256"/>
-      <c r="O13" s="256"/>
-      <c r="P13" s="256"/>
-      <c r="Q13" s="256"/>
-      <c r="R13" s="256"/>
+      <c r="D13" s="268"/>
+      <c r="E13" s="268"/>
+      <c r="F13" s="268"/>
+      <c r="G13" s="268"/>
+      <c r="H13" s="268"/>
+      <c r="I13" s="268"/>
+      <c r="J13" s="268"/>
+      <c r="K13" s="268"/>
+      <c r="L13" s="268"/>
+      <c r="M13" s="268"/>
+      <c r="N13" s="268"/>
+      <c r="O13" s="268"/>
+      <c r="P13" s="268"/>
+      <c r="Q13" s="268"/>
+      <c r="R13" s="268"/>
       <c r="S13" s="6"/>
     </row>
     <row r="14" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
-      <c r="D14" s="256"/>
-      <c r="E14" s="256"/>
-      <c r="F14" s="256"/>
-      <c r="G14" s="256"/>
-      <c r="H14" s="256"/>
-      <c r="I14" s="256"/>
-      <c r="J14" s="256"/>
-      <c r="K14" s="256"/>
-      <c r="L14" s="256"/>
-      <c r="M14" s="256"/>
-      <c r="N14" s="256"/>
-      <c r="O14" s="256"/>
-      <c r="P14" s="256"/>
-      <c r="Q14" s="256"/>
-      <c r="R14" s="256"/>
+      <c r="D14" s="268"/>
+      <c r="E14" s="268"/>
+      <c r="F14" s="268"/>
+      <c r="G14" s="268"/>
+      <c r="H14" s="268"/>
+      <c r="I14" s="268"/>
+      <c r="J14" s="268"/>
+      <c r="K14" s="268"/>
+      <c r="L14" s="268"/>
+      <c r="M14" s="268"/>
+      <c r="N14" s="268"/>
+      <c r="O14" s="268"/>
+      <c r="P14" s="268"/>
+      <c r="Q14" s="268"/>
+      <c r="R14" s="268"/>
       <c r="S14" s="6"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B15" s="4"/>
       <c r="C15" s="5"/>
-      <c r="D15" s="256"/>
-      <c r="E15" s="256"/>
-      <c r="F15" s="256"/>
-      <c r="G15" s="256"/>
-      <c r="H15" s="256"/>
-      <c r="I15" s="256"/>
-      <c r="J15" s="256"/>
-      <c r="K15" s="256"/>
-      <c r="L15" s="256"/>
-      <c r="M15" s="256"/>
-      <c r="N15" s="256"/>
-      <c r="O15" s="256"/>
-      <c r="P15" s="256"/>
-      <c r="Q15" s="256"/>
-      <c r="R15" s="256"/>
+      <c r="D15" s="268"/>
+      <c r="E15" s="268"/>
+      <c r="F15" s="268"/>
+      <c r="G15" s="268"/>
+      <c r="H15" s="268"/>
+      <c r="I15" s="268"/>
+      <c r="J15" s="268"/>
+      <c r="K15" s="268"/>
+      <c r="L15" s="268"/>
+      <c r="M15" s="268"/>
+      <c r="N15" s="268"/>
+      <c r="O15" s="268"/>
+      <c r="P15" s="268"/>
+      <c r="Q15" s="268"/>
+      <c r="R15" s="268"/>
       <c r="S15" s="6"/>
     </row>
     <row r="16" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
-      <c r="D16" s="256"/>
-      <c r="E16" s="256"/>
-      <c r="F16" s="256"/>
-      <c r="G16" s="256"/>
-      <c r="H16" s="256"/>
-      <c r="I16" s="256"/>
-      <c r="J16" s="256"/>
-      <c r="K16" s="256"/>
-      <c r="L16" s="256"/>
-      <c r="M16" s="256"/>
-      <c r="N16" s="256"/>
-      <c r="O16" s="256"/>
-      <c r="P16" s="256"/>
-      <c r="Q16" s="256"/>
-      <c r="R16" s="256"/>
+      <c r="D16" s="268"/>
+      <c r="E16" s="268"/>
+      <c r="F16" s="268"/>
+      <c r="G16" s="268"/>
+      <c r="H16" s="268"/>
+      <c r="I16" s="268"/>
+      <c r="J16" s="268"/>
+      <c r="K16" s="268"/>
+      <c r="L16" s="268"/>
+      <c r="M16" s="268"/>
+      <c r="N16" s="268"/>
+      <c r="O16" s="268"/>
+      <c r="P16" s="268"/>
+      <c r="Q16" s="268"/>
+      <c r="R16" s="268"/>
       <c r="S16" s="6"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A17" s="266" t="str">
+      <c r="A17" s="249" t="str">
         <f>IFERROR(HLOOKUP(LANGUAGE,DICCIONARIO!F1:K20,20,0),LANGUAGE)</f>
         <v>PERSONALIZAR DICCIONARIO</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
-      <c r="D17" s="256"/>
-      <c r="E17" s="256"/>
-      <c r="F17" s="256"/>
-      <c r="G17" s="256"/>
-      <c r="H17" s="256"/>
-      <c r="I17" s="256"/>
-      <c r="J17" s="256"/>
-      <c r="K17" s="256"/>
-      <c r="L17" s="256"/>
-      <c r="M17" s="256"/>
-      <c r="N17" s="256"/>
-      <c r="O17" s="256"/>
-      <c r="P17" s="256"/>
-      <c r="Q17" s="256"/>
-      <c r="R17" s="256"/>
+      <c r="D17" s="268"/>
+      <c r="E17" s="268"/>
+      <c r="F17" s="268"/>
+      <c r="G17" s="268"/>
+      <c r="H17" s="268"/>
+      <c r="I17" s="268"/>
+      <c r="J17" s="268"/>
+      <c r="K17" s="268"/>
+      <c r="L17" s="268"/>
+      <c r="M17" s="268"/>
+      <c r="N17" s="268"/>
+      <c r="O17" s="268"/>
+      <c r="P17" s="268"/>
+      <c r="Q17" s="268"/>
+      <c r="R17" s="268"/>
       <c r="S17" s="6"/>
     </row>
     <row r="18" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="266"/>
+      <c r="A18" s="249"/>
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
-      <c r="D18" s="256"/>
-      <c r="E18" s="256"/>
-      <c r="F18" s="256"/>
-      <c r="G18" s="256"/>
-      <c r="H18" s="256"/>
-      <c r="I18" s="256"/>
-      <c r="J18" s="256"/>
-      <c r="K18" s="256"/>
-      <c r="L18" s="256"/>
-      <c r="M18" s="256"/>
-      <c r="N18" s="256"/>
-      <c r="O18" s="256"/>
-      <c r="P18" s="256"/>
-      <c r="Q18" s="256"/>
-      <c r="R18" s="256"/>
+      <c r="D18" s="268"/>
+      <c r="E18" s="268"/>
+      <c r="F18" s="268"/>
+      <c r="G18" s="268"/>
+      <c r="H18" s="268"/>
+      <c r="I18" s="268"/>
+      <c r="J18" s="268"/>
+      <c r="K18" s="268"/>
+      <c r="L18" s="268"/>
+      <c r="M18" s="268"/>
+      <c r="N18" s="268"/>
+      <c r="O18" s="268"/>
+      <c r="P18" s="268"/>
+      <c r="Q18" s="268"/>
+      <c r="R18" s="268"/>
       <c r="S18" s="6"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A19" s="266"/>
+      <c r="A19" s="249"/>
       <c r="B19" s="4"/>
       <c r="C19" s="5"/>
-      <c r="D19" s="256"/>
-      <c r="E19" s="256"/>
-      <c r="F19" s="256"/>
-      <c r="G19" s="256"/>
-      <c r="H19" s="256"/>
-      <c r="I19" s="256"/>
-      <c r="J19" s="256"/>
-      <c r="K19" s="256"/>
-      <c r="L19" s="256"/>
-      <c r="M19" s="256"/>
-      <c r="N19" s="256"/>
-      <c r="O19" s="256"/>
-      <c r="P19" s="256"/>
-      <c r="Q19" s="256"/>
-      <c r="R19" s="256"/>
+      <c r="D19" s="268"/>
+      <c r="E19" s="268"/>
+      <c r="F19" s="268"/>
+      <c r="G19" s="268"/>
+      <c r="H19" s="268"/>
+      <c r="I19" s="268"/>
+      <c r="J19" s="268"/>
+      <c r="K19" s="268"/>
+      <c r="L19" s="268"/>
+      <c r="M19" s="268"/>
+      <c r="N19" s="268"/>
+      <c r="O19" s="268"/>
+      <c r="P19" s="268"/>
+      <c r="Q19" s="268"/>
+      <c r="R19" s="268"/>
       <c r="S19" s="6"/>
     </row>
     <row r="20" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B20" s="4"/>
       <c r="C20" s="5"/>
-      <c r="D20" s="256"/>
-      <c r="E20" s="256"/>
-      <c r="F20" s="256"/>
-      <c r="G20" s="256"/>
-      <c r="H20" s="256"/>
-      <c r="I20" s="256"/>
-      <c r="J20" s="256"/>
-      <c r="K20" s="256"/>
-      <c r="L20" s="256"/>
-      <c r="M20" s="256"/>
-      <c r="N20" s="256"/>
-      <c r="O20" s="256"/>
-      <c r="P20" s="256"/>
-      <c r="Q20" s="256"/>
-      <c r="R20" s="256"/>
+      <c r="D20" s="268"/>
+      <c r="E20" s="268"/>
+      <c r="F20" s="268"/>
+      <c r="G20" s="268"/>
+      <c r="H20" s="268"/>
+      <c r="I20" s="268"/>
+      <c r="J20" s="268"/>
+      <c r="K20" s="268"/>
+      <c r="L20" s="268"/>
+      <c r="M20" s="268"/>
+      <c r="N20" s="268"/>
+      <c r="O20" s="268"/>
+      <c r="P20" s="268"/>
+      <c r="Q20" s="268"/>
+      <c r="R20" s="268"/>
       <c r="S20" s="6"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B21" s="4"/>
       <c r="C21" s="5"/>
-      <c r="D21" s="256"/>
-      <c r="E21" s="256"/>
-      <c r="F21" s="256"/>
-      <c r="G21" s="256"/>
-      <c r="H21" s="256"/>
-      <c r="I21" s="256"/>
-      <c r="J21" s="256"/>
-      <c r="K21" s="256"/>
-      <c r="L21" s="256"/>
-      <c r="M21" s="256"/>
-      <c r="N21" s="256"/>
-      <c r="O21" s="256"/>
-      <c r="P21" s="256"/>
-      <c r="Q21" s="256"/>
-      <c r="R21" s="256"/>
+      <c r="D21" s="268"/>
+      <c r="E21" s="268"/>
+      <c r="F21" s="268"/>
+      <c r="G21" s="268"/>
+      <c r="H21" s="268"/>
+      <c r="I21" s="268"/>
+      <c r="J21" s="268"/>
+      <c r="K21" s="268"/>
+      <c r="L21" s="268"/>
+      <c r="M21" s="268"/>
+      <c r="N21" s="268"/>
+      <c r="O21" s="268"/>
+      <c r="P21" s="268"/>
+      <c r="Q21" s="268"/>
+      <c r="R21" s="268"/>
       <c r="S21" s="6"/>
     </row>
     <row r="22" spans="1:19" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -22300,42 +22361,42 @@
     </row>
     <row r="23" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="4"/>
-      <c r="C23" s="257" t="str">
+      <c r="C23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_10_"&amp;IDIOMA)</f>
         <v>OM 1R</v>
       </c>
-      <c r="D23" s="258"/>
-      <c r="E23" s="257" t="str">
+      <c r="D23" s="269"/>
+      <c r="E23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_11_"&amp;IDIOMA)</f>
         <v>OM +R</v>
       </c>
       <c r="F23" s="259"/>
-      <c r="G23" s="257" t="str">
+      <c r="G23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_12_"&amp;IDIOMA)</f>
         <v>VF</v>
       </c>
       <c r="H23" s="259"/>
-      <c r="I23" s="257" t="str">
+      <c r="I23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_13_"&amp;IDIOMA)</f>
         <v>EM</v>
       </c>
-      <c r="J23" s="258"/>
-      <c r="K23" s="257" t="str">
+      <c r="J23" s="269"/>
+      <c r="K23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_14_"&amp;IDIOMA)</f>
         <v>RC</v>
       </c>
       <c r="L23" s="259"/>
-      <c r="M23" s="257" t="str">
+      <c r="M23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_15_"&amp;IDIOMA)</f>
         <v>PP</v>
       </c>
       <c r="N23" s="259"/>
-      <c r="O23" s="257" t="str">
+      <c r="O23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_31_"&amp;IDIOMA)</f>
         <v>EN</v>
       </c>
       <c r="P23" s="259"/>
-      <c r="Q23" s="257" t="str">
+      <c r="Q23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_16_"&amp;IDIOMA)</f>
         <v>CL</v>
       </c>
@@ -22344,128 +22405,128 @@
     </row>
     <row r="24" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B24" s="4"/>
-      <c r="C24" s="248" t="str">
+      <c r="C24" s="275" t="str">
         <f ca="1">INDIRECT("Z_IN_08_"&amp;IDIOMA)</f>
         <v xml:space="preserve">Opción Múltiple 1R </v>
       </c>
-      <c r="D24" s="249"/>
-      <c r="E24" s="249" t="str">
+      <c r="D24" s="260"/>
+      <c r="E24" s="260" t="str">
         <f ca="1">INDIRECT("Z_IN_09_"&amp;IDIOMA)</f>
         <v xml:space="preserve">Opción Múltiple +R </v>
       </c>
-      <c r="F24" s="249"/>
-      <c r="G24" s="249" t="str">
+      <c r="F24" s="260"/>
+      <c r="G24" s="260" t="str">
         <f ca="1">INDIRECT("Z_IN_10_"&amp;IDIOMA)</f>
         <v>Verdadero/Falso</v>
       </c>
-      <c r="H24" s="249"/>
-      <c r="I24" s="249" t="str">
+      <c r="H24" s="260"/>
+      <c r="I24" s="260" t="str">
         <f ca="1">INDIRECT("Z_IN_11_"&amp;IDIOMA)</f>
         <v>Emparejar</v>
       </c>
-      <c r="J24" s="249"/>
-      <c r="K24" s="249" t="str">
+      <c r="J24" s="260"/>
+      <c r="K24" s="260" t="str">
         <f ca="1">INDIRECT("Z_IN_12_"&amp;IDIOMA)</f>
         <v>Respuesta Corta</v>
       </c>
-      <c r="L24" s="249"/>
-      <c r="M24" s="249" t="str">
+      <c r="L24" s="260"/>
+      <c r="M24" s="260" t="str">
         <f ca="1">INDIRECT("Z_IN_13_"&amp;IDIOMA)</f>
         <v>Palabra Perdida</v>
       </c>
-      <c r="N24" s="249"/>
-      <c r="O24" s="249" t="str">
+      <c r="N24" s="260"/>
+      <c r="O24" s="260" t="str">
         <f ca="1">INDIRECT("Z_IN_16_"&amp;IDIOMA)</f>
         <v>Ensayo</v>
       </c>
-      <c r="P24" s="249"/>
-      <c r="Q24" s="249" t="str">
+      <c r="P24" s="260"/>
+      <c r="Q24" s="260" t="str">
         <f ca="1">INDIRECT("Z_IN_14_"&amp;IDIOMA)</f>
         <v>Cloze</v>
       </c>
-      <c r="R24" s="274"/>
+      <c r="R24" s="262"/>
       <c r="S24" s="6"/>
     </row>
     <row r="25" spans="1:19" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="4"/>
-      <c r="C25" s="250"/>
-      <c r="D25" s="251"/>
-      <c r="E25" s="251"/>
-      <c r="F25" s="251"/>
-      <c r="G25" s="251"/>
-      <c r="H25" s="251"/>
-      <c r="I25" s="251"/>
-      <c r="J25" s="251"/>
-      <c r="K25" s="251"/>
-      <c r="L25" s="251"/>
-      <c r="M25" s="251"/>
-      <c r="N25" s="251"/>
-      <c r="O25" s="251"/>
-      <c r="P25" s="251"/>
-      <c r="Q25" s="251"/>
-      <c r="R25" s="275"/>
+      <c r="C25" s="276"/>
+      <c r="D25" s="261"/>
+      <c r="E25" s="261"/>
+      <c r="F25" s="261"/>
+      <c r="G25" s="261"/>
+      <c r="H25" s="261"/>
+      <c r="I25" s="261"/>
+      <c r="J25" s="261"/>
+      <c r="K25" s="261"/>
+      <c r="L25" s="261"/>
+      <c r="M25" s="261"/>
+      <c r="N25" s="261"/>
+      <c r="O25" s="261"/>
+      <c r="P25" s="261"/>
+      <c r="Q25" s="261"/>
+      <c r="R25" s="263"/>
       <c r="S25" s="6"/>
     </row>
     <row r="26" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="4"/>
-      <c r="C26" s="245" t="str">
+      <c r="C26" s="272" t="str">
         <f ca="1">'Datos OM'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>10 Preguntas</v>
       </c>
-      <c r="D26" s="247"/>
-      <c r="E26" s="245" t="str">
+      <c r="D26" s="274"/>
+      <c r="E26" s="272" t="str">
         <f ca="1">'Datos O2'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>10 Preguntas</v>
       </c>
-      <c r="F26" s="246"/>
-      <c r="G26" s="245" t="str">
+      <c r="F26" s="273"/>
+      <c r="G26" s="272" t="str">
         <f ca="1">'Datos VF'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>10 Preguntas</v>
       </c>
-      <c r="H26" s="246"/>
-      <c r="I26" s="245" t="str">
+      <c r="H26" s="273"/>
+      <c r="I26" s="272" t="str">
         <f ca="1">'Datos EM'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>10 Preguntas</v>
       </c>
-      <c r="J26" s="247"/>
-      <c r="K26" s="245" t="str">
+      <c r="J26" s="274"/>
+      <c r="K26" s="272" t="str">
         <f ca="1">'Datos RC'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>10 Preguntas</v>
       </c>
-      <c r="L26" s="246"/>
-      <c r="M26" s="245" t="str">
+      <c r="L26" s="273"/>
+      <c r="M26" s="272" t="str">
         <f ca="1">'Datos PP'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>10 Preguntas</v>
       </c>
-      <c r="N26" s="246"/>
-      <c r="O26" s="245" t="str">
+      <c r="N26" s="273"/>
+      <c r="O26" s="272" t="str">
         <f ca="1">'Datos EN'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>10 Preguntas</v>
       </c>
-      <c r="P26" s="246"/>
-      <c r="Q26" s="245" t="str">
+      <c r="P26" s="273"/>
+      <c r="Q26" s="272" t="str">
         <f ca="1">'Datos CL'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>10 Preguntas</v>
       </c>
-      <c r="R26" s="246"/>
+      <c r="R26" s="273"/>
       <c r="S26" s="6"/>
     </row>
     <row r="27" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="267" t="str">
+      <c r="D27" s="250" t="str">
         <f ca="1">INDIRECT("Z_IN_07_"&amp;IDIOMA)</f>
         <v>Esta HOJA sirve para almacenar las preguntas y poder reutilizarlas cuando sea necesario, sin tener que volver a escribirlas para un nuevo BANCO DE PREGUNTAS.</v>
       </c>
-      <c r="E27" s="267"/>
-      <c r="F27" s="267"/>
-      <c r="G27" s="267"/>
-      <c r="H27" s="267"/>
-      <c r="I27" s="267"/>
-      <c r="J27" s="267"/>
-      <c r="K27" s="267"/>
-      <c r="L27" s="267"/>
-      <c r="M27" s="267"/>
+      <c r="E27" s="250"/>
+      <c r="F27" s="250"/>
+      <c r="G27" s="250"/>
+      <c r="H27" s="250"/>
+      <c r="I27" s="250"/>
+      <c r="J27" s="250"/>
+      <c r="K27" s="250"/>
+      <c r="L27" s="250"/>
+      <c r="M27" s="250"/>
       <c r="N27" s="144"/>
       <c r="O27" s="7"/>
       <c r="P27" s="7"/>
@@ -22476,141 +22537,141 @@
     <row r="28" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="268"/>
-      <c r="E28" s="268"/>
-      <c r="F28" s="268"/>
-      <c r="G28" s="268"/>
-      <c r="H28" s="268"/>
-      <c r="I28" s="268"/>
-      <c r="J28" s="268"/>
-      <c r="K28" s="268"/>
-      <c r="L28" s="268"/>
-      <c r="M28" s="268"/>
+      <c r="D28" s="251"/>
+      <c r="E28" s="251"/>
+      <c r="F28" s="251"/>
+      <c r="G28" s="251"/>
+      <c r="H28" s="251"/>
+      <c r="I28" s="251"/>
+      <c r="J28" s="251"/>
+      <c r="K28" s="251"/>
+      <c r="L28" s="251"/>
+      <c r="M28" s="251"/>
       <c r="N28" s="145"/>
       <c r="O28" s="5"/>
-      <c r="P28" s="244"/>
-      <c r="Q28" s="244"/>
-      <c r="R28" s="244"/>
+      <c r="P28" s="252"/>
+      <c r="Q28" s="252"/>
+      <c r="R28" s="252"/>
       <c r="S28" s="6"/>
     </row>
     <row r="29" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="268"/>
-      <c r="E29" s="268"/>
-      <c r="F29" s="268"/>
-      <c r="G29" s="268"/>
-      <c r="H29" s="268"/>
-      <c r="I29" s="268"/>
-      <c r="J29" s="268"/>
-      <c r="K29" s="268"/>
-      <c r="L29" s="268"/>
-      <c r="M29" s="268"/>
+      <c r="D29" s="251"/>
+      <c r="E29" s="251"/>
+      <c r="F29" s="251"/>
+      <c r="G29" s="251"/>
+      <c r="H29" s="251"/>
+      <c r="I29" s="251"/>
+      <c r="J29" s="251"/>
+      <c r="K29" s="251"/>
+      <c r="L29" s="251"/>
+      <c r="M29" s="251"/>
       <c r="N29" s="145"/>
       <c r="O29" s="5"/>
-      <c r="P29" s="244"/>
-      <c r="Q29" s="244"/>
-      <c r="R29" s="244"/>
+      <c r="P29" s="252"/>
+      <c r="Q29" s="252"/>
+      <c r="R29" s="252"/>
       <c r="S29" s="6"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="268"/>
-      <c r="E30" s="268"/>
-      <c r="F30" s="268"/>
-      <c r="G30" s="268"/>
-      <c r="H30" s="268"/>
-      <c r="I30" s="268"/>
-      <c r="J30" s="268"/>
-      <c r="K30" s="268"/>
-      <c r="L30" s="268"/>
-      <c r="M30" s="268"/>
+      <c r="D30" s="251"/>
+      <c r="E30" s="251"/>
+      <c r="F30" s="251"/>
+      <c r="G30" s="251"/>
+      <c r="H30" s="251"/>
+      <c r="I30" s="251"/>
+      <c r="J30" s="251"/>
+      <c r="K30" s="251"/>
+      <c r="L30" s="251"/>
+      <c r="M30" s="251"/>
       <c r="N30" s="145"/>
       <c r="O30" s="5"/>
-      <c r="P30" s="244"/>
-      <c r="Q30" s="244"/>
-      <c r="R30" s="244"/>
+      <c r="P30" s="252"/>
+      <c r="Q30" s="252"/>
+      <c r="R30" s="252"/>
       <c r="S30" s="6"/>
     </row>
     <row r="31" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B31" s="4"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="268"/>
-      <c r="E31" s="268"/>
-      <c r="F31" s="268"/>
-      <c r="G31" s="268"/>
-      <c r="H31" s="268"/>
-      <c r="I31" s="268"/>
-      <c r="J31" s="268"/>
-      <c r="K31" s="268"/>
-      <c r="L31" s="268"/>
-      <c r="M31" s="268"/>
+      <c r="D31" s="251"/>
+      <c r="E31" s="251"/>
+      <c r="F31" s="251"/>
+      <c r="G31" s="251"/>
+      <c r="H31" s="251"/>
+      <c r="I31" s="251"/>
+      <c r="J31" s="251"/>
+      <c r="K31" s="251"/>
+      <c r="L31" s="251"/>
+      <c r="M31" s="251"/>
       <c r="N31" s="145"/>
       <c r="O31" s="5"/>
-      <c r="P31" s="244"/>
-      <c r="Q31" s="244"/>
-      <c r="R31" s="244"/>
+      <c r="P31" s="252"/>
+      <c r="Q31" s="252"/>
+      <c r="R31" s="252"/>
       <c r="S31" s="6"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B32" s="4"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="268"/>
-      <c r="E32" s="268"/>
-      <c r="F32" s="268"/>
-      <c r="G32" s="268"/>
-      <c r="H32" s="268"/>
-      <c r="I32" s="268"/>
-      <c r="J32" s="268"/>
-      <c r="K32" s="268"/>
-      <c r="L32" s="268"/>
-      <c r="M32" s="268"/>
+      <c r="D32" s="251"/>
+      <c r="E32" s="251"/>
+      <c r="F32" s="251"/>
+      <c r="G32" s="251"/>
+      <c r="H32" s="251"/>
+      <c r="I32" s="251"/>
+      <c r="J32" s="251"/>
+      <c r="K32" s="251"/>
+      <c r="L32" s="251"/>
+      <c r="M32" s="251"/>
       <c r="N32" s="145"/>
       <c r="O32" s="5"/>
-      <c r="P32" s="244"/>
-      <c r="Q32" s="244"/>
-      <c r="R32" s="244"/>
+      <c r="P32" s="252"/>
+      <c r="Q32" s="252"/>
+      <c r="R32" s="252"/>
       <c r="S32" s="6"/>
     </row>
     <row r="33" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B33" s="4"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="268"/>
-      <c r="E33" s="268"/>
-      <c r="F33" s="268"/>
-      <c r="G33" s="268"/>
-      <c r="H33" s="268"/>
-      <c r="I33" s="268"/>
-      <c r="J33" s="268"/>
-      <c r="K33" s="268"/>
-      <c r="L33" s="268"/>
-      <c r="M33" s="268"/>
+      <c r="D33" s="251"/>
+      <c r="E33" s="251"/>
+      <c r="F33" s="251"/>
+      <c r="G33" s="251"/>
+      <c r="H33" s="251"/>
+      <c r="I33" s="251"/>
+      <c r="J33" s="251"/>
+      <c r="K33" s="251"/>
+      <c r="L33" s="251"/>
+      <c r="M33" s="251"/>
       <c r="N33" s="145"/>
       <c r="O33" s="5"/>
-      <c r="P33" s="244"/>
-      <c r="Q33" s="244"/>
-      <c r="R33" s="244"/>
+      <c r="P33" s="252"/>
+      <c r="Q33" s="252"/>
+      <c r="R33" s="252"/>
       <c r="S33" s="6"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
-      <c r="D34" s="268"/>
-      <c r="E34" s="268"/>
-      <c r="F34" s="268"/>
-      <c r="G34" s="268"/>
-      <c r="H34" s="268"/>
-      <c r="I34" s="268"/>
-      <c r="J34" s="268"/>
-      <c r="K34" s="268"/>
-      <c r="L34" s="268"/>
-      <c r="M34" s="268"/>
+      <c r="D34" s="251"/>
+      <c r="E34" s="251"/>
+      <c r="F34" s="251"/>
+      <c r="G34" s="251"/>
+      <c r="H34" s="251"/>
+      <c r="I34" s="251"/>
+      <c r="J34" s="251"/>
+      <c r="K34" s="251"/>
+      <c r="L34" s="251"/>
+      <c r="M34" s="251"/>
       <c r="N34" s="145"/>
       <c r="O34" s="5"/>
-      <c r="P34" s="244"/>
-      <c r="Q34" s="244"/>
-      <c r="R34" s="244"/>
+      <c r="P34" s="252"/>
+      <c r="Q34" s="252"/>
+      <c r="R34" s="252"/>
       <c r="S34" s="6"/>
     </row>
     <row r="35" spans="1:19" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -22725,8 +22786,34 @@
     </row>
     <row r="47" spans="1:19" ht="5.0999999999999996" customHeight="1" thickTop="1" x14ac:dyDescent="0.5"/>
   </sheetData>
-  <sheetProtection selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="7mJcO9X2qeaCviAZjnqSLLaA9Vzz33+gGgB5Mj6YuUDC92xAaPlLfOrVWHMUYnY1q8J3UamvkNKCDXHYt1Y7RA==" saltValue="PAD9h1JukXOCEfMZ/TfD9Q==" spinCount="100000" sheet="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="42">
+    <mergeCell ref="P28:R29"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="E24:F25"/>
+    <mergeCell ref="G24:H25"/>
+    <mergeCell ref="I24:J25"/>
+    <mergeCell ref="K24:L25"/>
+    <mergeCell ref="O24:P25"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B1:S1"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="D11:R21"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="N5:O10"/>
+    <mergeCell ref="F5:G10"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A1:A9"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A17:A19"/>
@@ -22743,32 +22830,6 @@
     <mergeCell ref="Q23:R23"/>
     <mergeCell ref="M24:N25"/>
     <mergeCell ref="Q24:R25"/>
-    <mergeCell ref="B1:S1"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="D11:R21"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="N5:O10"/>
-    <mergeCell ref="F5:G10"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="P28:R29"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="E24:F25"/>
-    <mergeCell ref="G24:H25"/>
-    <mergeCell ref="I24:J25"/>
-    <mergeCell ref="K24:L25"/>
-    <mergeCell ref="O24:P25"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A11:A13" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -27918,13 +27979,13 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="EFvDi3MSRW73NdIsYvAsc+BhgNAxKxcPxTt3ACKCjR73QNbhqIfRpAgCELXZUjGGqLKgcIubArfstFoT9O9iow==" saltValue="M4mqjZOIoId7mfBIEVvyPQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="F3:F53 F55">
-    <cfRule type="duplicateValues" dxfId="43" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="duplicateValues" dxfId="42" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F56:F66">
-    <cfRule type="duplicateValues" dxfId="41" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W38:W43 X3:X29" xr:uid="{00000000-0002-0000-0900-000000000000}">
@@ -28032,7 +28093,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!C24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - OPCIÓN MÚLTIPLE 1R 
+        <v>FastTest PlugIn - V8.3  - OPCIÓN MÚLTIPLE 1R 
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="67" t="str">
@@ -28251,42 +28312,42 @@
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="77" t="s">
+        <v>831</v>
+      </c>
+      <c r="F5" s="76" t="s">
         <v>832</v>
       </c>
-      <c r="F5" s="76" t="s">
+      <c r="G5" s="12" t="s">
         <v>833</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="H5" s="13" t="s">
         <v>834</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="I5" s="14" t="s">
         <v>835</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="J5" s="15" t="s">
         <v>836</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>837</v>
       </c>
       <c r="K5" s="16"/>
       <c r="L5" s="17"/>
       <c r="M5" s="24" t="s">
+        <v>837</v>
+      </c>
+      <c r="N5" s="25" t="s">
         <v>838</v>
       </c>
-      <c r="N5" s="25" t="s">
-        <v>839</v>
-      </c>
       <c r="O5" s="26" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="P5" s="27" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="Q5" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R5" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S5" s="24">
         <v>100</v>
@@ -28301,10 +28362,10 @@
         <v>0</v>
       </c>
       <c r="W5" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X5" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y5" s="29"/>
       <c r="Z5" s="29"/>
@@ -28313,19 +28374,19 @@
       <c r="AC5" s="29"/>
       <c r="AD5" s="29"/>
       <c r="AE5" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF5" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG5" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH5" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI5" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.5">
@@ -28339,42 +28400,42 @@
       </c>
       <c r="D6" s="23"/>
       <c r="E6" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F6" s="76" t="s">
+        <v>840</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>841</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="H6" s="13" t="s">
         <v>842</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="I6" s="14" t="s">
         <v>843</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="J6" s="15" t="s">
         <v>844</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>845</v>
       </c>
       <c r="K6" s="16"/>
       <c r="L6" s="17"/>
       <c r="M6" s="24" t="s">
+        <v>837</v>
+      </c>
+      <c r="N6" s="25" t="s">
         <v>838</v>
       </c>
-      <c r="N6" s="25" t="s">
-        <v>839</v>
-      </c>
       <c r="O6" s="26" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="P6" s="27" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="Q6" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R6" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S6" s="24">
         <v>100</v>
@@ -28389,10 +28450,10 @@
         <v>0</v>
       </c>
       <c r="W6" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X6" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y6" s="29"/>
       <c r="Z6" s="29"/>
@@ -28401,19 +28462,19 @@
       <c r="AC6" s="29"/>
       <c r="AD6" s="29"/>
       <c r="AE6" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF6" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG6" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI6" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.5">
@@ -28427,42 +28488,42 @@
       </c>
       <c r="D7" s="23"/>
       <c r="E7" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F7" s="76" t="s">
+        <v>845</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>846</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="H7" s="13" t="s">
         <v>847</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="I7" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="J7" s="15" t="s">
         <v>849</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>850</v>
       </c>
       <c r="K7" s="16"/>
       <c r="L7" s="17"/>
       <c r="M7" s="24" t="s">
+        <v>837</v>
+      </c>
+      <c r="N7" s="25" t="s">
         <v>838</v>
       </c>
-      <c r="N7" s="25" t="s">
-        <v>839</v>
-      </c>
       <c r="O7" s="26" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="P7" s="27" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="Q7" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R7" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S7" s="24">
         <v>100</v>
@@ -28477,10 +28538,10 @@
         <v>0</v>
       </c>
       <c r="W7" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X7" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y7" s="29"/>
       <c r="Z7" s="29"/>
@@ -28489,19 +28550,19 @@
       <c r="AC7" s="29"/>
       <c r="AD7" s="29"/>
       <c r="AE7" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF7" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG7" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH7" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI7" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.5">
@@ -28515,42 +28576,42 @@
       </c>
       <c r="D8" s="23"/>
       <c r="E8" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F8" s="76" t="s">
+        <v>850</v>
+      </c>
+      <c r="G8" s="12" t="s">
         <v>851</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="H8" s="13" t="s">
         <v>852</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="I8" s="14" t="s">
         <v>853</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="J8" s="15" t="s">
         <v>854</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>855</v>
       </c>
       <c r="K8" s="16"/>
       <c r="L8" s="17"/>
       <c r="M8" s="24" t="s">
+        <v>837</v>
+      </c>
+      <c r="N8" s="25" t="s">
         <v>838</v>
       </c>
-      <c r="N8" s="25" t="s">
-        <v>839</v>
-      </c>
       <c r="O8" s="26" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="P8" s="27" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="Q8" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R8" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S8" s="24">
         <v>100</v>
@@ -28565,10 +28626,10 @@
         <v>0</v>
       </c>
       <c r="W8" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X8" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y8" s="29"/>
       <c r="Z8" s="29"/>
@@ -28577,19 +28638,19 @@
       <c r="AC8" s="29"/>
       <c r="AD8" s="29"/>
       <c r="AE8" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF8" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG8" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH8" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI8" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.5">
@@ -28603,19 +28664,19 @@
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F9" s="76" t="s">
+        <v>855</v>
+      </c>
+      <c r="G9" s="12" t="s">
         <v>856</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="H9" s="13" t="s">
         <v>857</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="I9" s="14" t="s">
         <v>858</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>859</v>
       </c>
       <c r="J9" s="15" t="s">
         <v>160</v>
@@ -28623,22 +28684,22 @@
       <c r="K9" s="16"/>
       <c r="L9" s="17"/>
       <c r="M9" s="24" t="s">
+        <v>837</v>
+      </c>
+      <c r="N9" s="25" t="s">
         <v>838</v>
       </c>
-      <c r="N9" s="25" t="s">
-        <v>839</v>
-      </c>
       <c r="O9" s="26" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="P9" s="27" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="Q9" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R9" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S9" s="24">
         <v>100</v>
@@ -28653,10 +28714,10 @@
         <v>0</v>
       </c>
       <c r="W9" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X9" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y9" s="29"/>
       <c r="Z9" s="29"/>
@@ -28665,19 +28726,19 @@
       <c r="AC9" s="29"/>
       <c r="AD9" s="29"/>
       <c r="AE9" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF9" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG9" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH9" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI9" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.5">
@@ -28691,42 +28752,42 @@
       </c>
       <c r="D10" s="23"/>
       <c r="E10" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F10" s="76" t="s">
+        <v>859</v>
+      </c>
+      <c r="G10" s="12" t="s">
         <v>860</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="H10" s="13" t="s">
+        <v>842</v>
+      </c>
+      <c r="I10" s="14" t="s">
         <v>861</v>
       </c>
-      <c r="H10" s="13" t="s">
-        <v>843</v>
-      </c>
-      <c r="I10" s="14" t="s">
+      <c r="J10" s="15" t="s">
         <v>862</v>
-      </c>
-      <c r="J10" s="15" t="s">
-        <v>863</v>
       </c>
       <c r="K10" s="16"/>
       <c r="L10" s="17"/>
       <c r="M10" s="24" t="s">
+        <v>837</v>
+      </c>
+      <c r="N10" s="25" t="s">
         <v>838</v>
       </c>
-      <c r="N10" s="25" t="s">
-        <v>839</v>
-      </c>
       <c r="O10" s="26" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="P10" s="27" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="Q10" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R10" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S10" s="24">
         <v>100</v>
@@ -28741,10 +28802,10 @@
         <v>0</v>
       </c>
       <c r="W10" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X10" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y10" s="29"/>
       <c r="Z10" s="29"/>
@@ -28753,19 +28814,19 @@
       <c r="AC10" s="29"/>
       <c r="AD10" s="29"/>
       <c r="AE10" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF10" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG10" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH10" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI10" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.5">
@@ -28779,42 +28840,42 @@
       </c>
       <c r="D11" s="23"/>
       <c r="E11" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F11" s="76" t="s">
+        <v>863</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>861</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>843</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>847</v>
+      </c>
+      <c r="J11" s="15" t="s">
         <v>864</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>862</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>844</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>848</v>
-      </c>
-      <c r="J11" s="15" t="s">
-        <v>865</v>
       </c>
       <c r="K11" s="16"/>
       <c r="L11" s="17"/>
       <c r="M11" s="24" t="s">
+        <v>837</v>
+      </c>
+      <c r="N11" s="25" t="s">
         <v>838</v>
       </c>
-      <c r="N11" s="25" t="s">
-        <v>839</v>
-      </c>
       <c r="O11" s="26" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="P11" s="27" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="Q11" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R11" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S11" s="24">
         <v>100</v>
@@ -28829,10 +28890,10 @@
         <v>0</v>
       </c>
       <c r="W11" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X11" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y11" s="29"/>
       <c r="Z11" s="29"/>
@@ -28841,19 +28902,19 @@
       <c r="AC11" s="29"/>
       <c r="AD11" s="29"/>
       <c r="AE11" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF11" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG11" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH11" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI11" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.5">
@@ -28867,42 +28928,42 @@
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F12" s="76" t="s">
+        <v>865</v>
+      </c>
+      <c r="G12" s="12" t="s">
         <v>866</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="H12" s="13" t="s">
         <v>867</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="I12" s="14" t="s">
         <v>868</v>
       </c>
-      <c r="I12" s="14" t="s">
-        <v>869</v>
-      </c>
       <c r="J12" s="15" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="K12" s="16"/>
       <c r="L12" s="17"/>
       <c r="M12" s="24" t="s">
+        <v>837</v>
+      </c>
+      <c r="N12" s="25" t="s">
         <v>838</v>
       </c>
-      <c r="N12" s="25" t="s">
-        <v>839</v>
-      </c>
       <c r="O12" s="26" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="P12" s="27" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="Q12" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R12" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S12" s="24">
         <v>100</v>
@@ -28917,10 +28978,10 @@
         <v>0</v>
       </c>
       <c r="W12" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X12" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y12" s="29"/>
       <c r="Z12" s="29"/>
@@ -28929,19 +28990,19 @@
       <c r="AC12" s="29"/>
       <c r="AD12" s="29"/>
       <c r="AE12" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF12" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG12" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH12" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI12" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.5">
@@ -28955,42 +29016,42 @@
       </c>
       <c r="D13" s="23"/>
       <c r="E13" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F13" s="76" t="s">
+        <v>869</v>
+      </c>
+      <c r="G13" s="12" t="s">
         <v>870</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="H13" s="13" t="s">
         <v>871</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="I13" s="14" t="s">
+        <v>847</v>
+      </c>
+      <c r="J13" s="15" t="s">
         <v>872</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>848</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>873</v>
       </c>
       <c r="K13" s="16"/>
       <c r="L13" s="17"/>
       <c r="M13" s="24" t="s">
+        <v>837</v>
+      </c>
+      <c r="N13" s="25" t="s">
         <v>838</v>
       </c>
-      <c r="N13" s="25" t="s">
-        <v>839</v>
-      </c>
       <c r="O13" s="26" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="P13" s="27" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="Q13" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R13" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S13" s="24">
         <v>100</v>
@@ -29005,10 +29066,10 @@
         <v>0</v>
       </c>
       <c r="W13" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X13" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y13" s="29"/>
       <c r="Z13" s="29"/>
@@ -29017,19 +29078,19 @@
       <c r="AC13" s="29"/>
       <c r="AD13" s="29"/>
       <c r="AE13" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF13" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG13" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH13" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI13" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.5">
@@ -29043,42 +29104,42 @@
       </c>
       <c r="D14" s="23"/>
       <c r="E14" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F14" s="76" t="s">
+        <v>873</v>
+      </c>
+      <c r="G14" s="12" t="s">
         <v>874</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="H14" s="13" t="s">
+        <v>852</v>
+      </c>
+      <c r="I14" s="14" t="s">
         <v>875</v>
       </c>
-      <c r="H14" s="13" t="s">
-        <v>853</v>
-      </c>
-      <c r="I14" s="14" t="s">
+      <c r="J14" s="15" t="s">
         <v>876</v>
-      </c>
-      <c r="J14" s="15" t="s">
-        <v>877</v>
       </c>
       <c r="K14" s="16"/>
       <c r="L14" s="17"/>
       <c r="M14" s="24" t="s">
+        <v>837</v>
+      </c>
+      <c r="N14" s="25" t="s">
         <v>838</v>
       </c>
-      <c r="N14" s="25" t="s">
-        <v>839</v>
-      </c>
       <c r="O14" s="26" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="P14" s="27" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="Q14" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R14" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S14" s="24">
         <v>100</v>
@@ -29093,10 +29154,10 @@
         <v>0</v>
       </c>
       <c r="W14" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X14" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y14" s="29"/>
       <c r="Z14" s="29"/>
@@ -29105,19 +29166,19 @@
       <c r="AC14" s="29"/>
       <c r="AD14" s="29"/>
       <c r="AE14" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF14" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG14" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH14" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI14" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
   </sheetData>
@@ -29219,7 +29280,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!E24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - OPCIÓN MÚLTIPLE +R 
+        <v>FastTest PlugIn - V8.3  - OPCIÓN MÚLTIPLE +R 
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="67" t="str">
@@ -29442,42 +29503,42 @@
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F5" s="76" t="s">
+        <v>877</v>
+      </c>
+      <c r="G5" s="12" t="s">
         <v>878</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="H5" s="13" t="s">
         <v>879</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="I5" s="14" t="s">
         <v>880</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="J5" s="15" t="s">
         <v>881</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>882</v>
       </c>
       <c r="K5" s="16"/>
       <c r="L5" s="17"/>
       <c r="M5" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="N5" s="25" t="s">
+        <v>882</v>
+      </c>
+      <c r="O5" s="26" t="s">
         <v>883</v>
       </c>
-      <c r="N5" s="25" t="s">
+      <c r="P5" s="27" t="s">
         <v>883</v>
       </c>
-      <c r="O5" s="26" t="s">
-        <v>884</v>
-      </c>
-      <c r="P5" s="27" t="s">
-        <v>884</v>
-      </c>
       <c r="Q5" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R5" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S5" s="24">
         <v>50</v>
@@ -29486,37 +29547,39 @@
         <v>50</v>
       </c>
       <c r="U5" s="26" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V5" s="27" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W5" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X5" s="29" t="s">
-        <v>840</v>
-      </c>
-      <c r="Y5" s="199"/>
+        <v>839</v>
+      </c>
+      <c r="Y5" s="199">
+        <v>2</v>
+      </c>
       <c r="Z5" s="29"/>
       <c r="AA5" s="29"/>
       <c r="AB5" s="29"/>
       <c r="AC5" s="29"/>
       <c r="AD5" s="29"/>
       <c r="AE5" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF5" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG5" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH5" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI5" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.5">
@@ -29530,42 +29593,42 @@
       </c>
       <c r="D6" s="23"/>
       <c r="E6" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F6" s="151" t="s">
+        <v>884</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>885</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="H6" s="13" t="s">
         <v>886</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="I6" s="14" t="s">
         <v>887</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="J6" s="15" t="s">
         <v>888</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>889</v>
       </c>
       <c r="K6" s="16"/>
       <c r="L6" s="17"/>
       <c r="M6" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="N6" s="25" t="s">
+        <v>882</v>
+      </c>
+      <c r="O6" s="26" t="s">
         <v>883</v>
       </c>
-      <c r="N6" s="25" t="s">
+      <c r="P6" s="27" t="s">
         <v>883</v>
       </c>
-      <c r="O6" s="26" t="s">
-        <v>884</v>
-      </c>
-      <c r="P6" s="27" t="s">
-        <v>884</v>
-      </c>
       <c r="Q6" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R6" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S6" s="24">
         <v>50</v>
@@ -29574,37 +29637,39 @@
         <v>50</v>
       </c>
       <c r="U6" s="26" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V6" s="27" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W6" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X6" s="29" t="s">
-        <v>840</v>
-      </c>
-      <c r="Y6" s="199"/>
+        <v>839</v>
+      </c>
+      <c r="Y6" s="199">
+        <v>2</v>
+      </c>
       <c r="Z6" s="29"/>
       <c r="AA6" s="29"/>
       <c r="AB6" s="29"/>
       <c r="AC6" s="29"/>
       <c r="AD6" s="29"/>
       <c r="AE6" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF6" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG6" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI6" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.5">
@@ -29618,42 +29683,42 @@
       </c>
       <c r="D7" s="23"/>
       <c r="E7" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F7" s="151" t="s">
+        <v>889</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>890</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="H7" s="13" t="s">
+        <v>842</v>
+      </c>
+      <c r="I7" s="14" t="s">
         <v>891</v>
       </c>
-      <c r="H7" s="13" t="s">
-        <v>843</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>892</v>
-      </c>
       <c r="J7" s="15" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="K7" s="16"/>
       <c r="L7" s="17"/>
       <c r="M7" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="N7" s="25" t="s">
+        <v>882</v>
+      </c>
+      <c r="O7" s="26" t="s">
         <v>883</v>
       </c>
-      <c r="N7" s="25" t="s">
+      <c r="P7" s="27" t="s">
         <v>883</v>
       </c>
-      <c r="O7" s="26" t="s">
-        <v>884</v>
-      </c>
-      <c r="P7" s="27" t="s">
-        <v>884</v>
-      </c>
       <c r="Q7" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R7" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S7" s="24">
         <v>50</v>
@@ -29662,37 +29727,39 @@
         <v>50</v>
       </c>
       <c r="U7" s="26" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V7" s="27" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W7" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X7" s="29" t="s">
-        <v>840</v>
-      </c>
-      <c r="Y7" s="199"/>
+        <v>839</v>
+      </c>
+      <c r="Y7" s="199">
+        <v>2</v>
+      </c>
       <c r="Z7" s="29"/>
       <c r="AA7" s="29"/>
       <c r="AB7" s="29"/>
       <c r="AC7" s="29"/>
       <c r="AD7" s="29"/>
       <c r="AE7" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF7" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG7" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH7" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI7" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.5">
@@ -29706,42 +29773,42 @@
       </c>
       <c r="D8" s="23"/>
       <c r="E8" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F8" s="151" t="s">
+        <v>892</v>
+      </c>
+      <c r="G8" s="12" t="s">
         <v>893</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="H8" s="13" t="s">
         <v>894</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="I8" s="14" t="s">
         <v>895</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="J8" s="15" t="s">
         <v>896</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>897</v>
       </c>
       <c r="K8" s="16"/>
       <c r="L8" s="17"/>
       <c r="M8" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="N8" s="25" t="s">
+        <v>882</v>
+      </c>
+      <c r="O8" s="26" t="s">
         <v>883</v>
       </c>
-      <c r="N8" s="25" t="s">
+      <c r="P8" s="27" t="s">
         <v>883</v>
       </c>
-      <c r="O8" s="26" t="s">
-        <v>884</v>
-      </c>
-      <c r="P8" s="27" t="s">
-        <v>884</v>
-      </c>
       <c r="Q8" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R8" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S8" s="24">
         <v>50</v>
@@ -29750,37 +29817,39 @@
         <v>50</v>
       </c>
       <c r="U8" s="26" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V8" s="27" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W8" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X8" s="29" t="s">
-        <v>840</v>
-      </c>
-      <c r="Y8" s="199"/>
+        <v>839</v>
+      </c>
+      <c r="Y8" s="199">
+        <v>2</v>
+      </c>
       <c r="Z8" s="29"/>
       <c r="AA8" s="29"/>
       <c r="AB8" s="29"/>
       <c r="AC8" s="29"/>
       <c r="AD8" s="29"/>
       <c r="AE8" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF8" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG8" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH8" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI8" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.5">
@@ -29794,42 +29863,42 @@
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F9" s="151" t="s">
+        <v>897</v>
+      </c>
+      <c r="G9" s="12" t="s">
         <v>898</v>
       </c>
-      <c r="G9" s="12" t="s">
-        <v>899</v>
-      </c>
       <c r="H9" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="K9" s="16"/>
       <c r="L9" s="17"/>
       <c r="M9" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="N9" s="25" t="s">
+        <v>882</v>
+      </c>
+      <c r="O9" s="26" t="s">
         <v>883</v>
       </c>
-      <c r="N9" s="25" t="s">
+      <c r="P9" s="27" t="s">
         <v>883</v>
       </c>
-      <c r="O9" s="26" t="s">
-        <v>884</v>
-      </c>
-      <c r="P9" s="27" t="s">
-        <v>884</v>
-      </c>
       <c r="Q9" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R9" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S9" s="24">
         <v>50</v>
@@ -29838,37 +29907,39 @@
         <v>50</v>
       </c>
       <c r="U9" s="26" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V9" s="27" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W9" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X9" s="29" t="s">
-        <v>840</v>
-      </c>
-      <c r="Y9" s="199"/>
+        <v>839</v>
+      </c>
+      <c r="Y9" s="199">
+        <v>2</v>
+      </c>
       <c r="Z9" s="29"/>
       <c r="AA9" s="29"/>
       <c r="AB9" s="29"/>
       <c r="AC9" s="29"/>
       <c r="AD9" s="29"/>
       <c r="AE9" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF9" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG9" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH9" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI9" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.5">
@@ -29882,42 +29953,42 @@
       </c>
       <c r="D10" s="23"/>
       <c r="E10" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F10" s="151" t="s">
+        <v>899</v>
+      </c>
+      <c r="G10" s="12" t="s">
         <v>900</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="H10" s="13" t="s">
         <v>901</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="I10" s="14" t="s">
         <v>902</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="J10" s="15" t="s">
         <v>903</v>
-      </c>
-      <c r="J10" s="15" t="s">
-        <v>904</v>
       </c>
       <c r="K10" s="16"/>
       <c r="L10" s="17"/>
       <c r="M10" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="N10" s="25" t="s">
+        <v>882</v>
+      </c>
+      <c r="O10" s="26" t="s">
         <v>883</v>
       </c>
-      <c r="N10" s="25" t="s">
+      <c r="P10" s="27" t="s">
         <v>883</v>
       </c>
-      <c r="O10" s="26" t="s">
-        <v>884</v>
-      </c>
-      <c r="P10" s="27" t="s">
-        <v>884</v>
-      </c>
       <c r="Q10" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R10" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S10" s="24">
         <v>50</v>
@@ -29926,16 +29997,16 @@
         <v>50</v>
       </c>
       <c r="U10" s="26" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V10" s="27" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W10" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X10" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y10" s="199"/>
       <c r="Z10" s="29"/>
@@ -29944,19 +30015,19 @@
       <c r="AC10" s="29"/>
       <c r="AD10" s="29"/>
       <c r="AE10" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF10" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG10" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH10" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI10" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.5">
@@ -29970,42 +30041,42 @@
       </c>
       <c r="D11" s="23"/>
       <c r="E11" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F11" s="151" t="s">
+        <v>904</v>
+      </c>
+      <c r="G11" s="12" t="s">
         <v>905</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="H11" s="13" t="s">
+        <v>893</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>846</v>
+      </c>
+      <c r="J11" s="15" t="s">
         <v>906</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>894</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>847</v>
-      </c>
-      <c r="J11" s="15" t="s">
-        <v>907</v>
       </c>
       <c r="K11" s="16"/>
       <c r="L11" s="17"/>
       <c r="M11" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="N11" s="25" t="s">
+        <v>882</v>
+      </c>
+      <c r="O11" s="26" t="s">
         <v>883</v>
       </c>
-      <c r="N11" s="25" t="s">
+      <c r="P11" s="27" t="s">
         <v>883</v>
       </c>
-      <c r="O11" s="26" t="s">
-        <v>884</v>
-      </c>
-      <c r="P11" s="27" t="s">
-        <v>884</v>
-      </c>
       <c r="Q11" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R11" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S11" s="24">
         <v>50</v>
@@ -30014,16 +30085,16 @@
         <v>50</v>
       </c>
       <c r="U11" s="26" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V11" s="27" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W11" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X11" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y11" s="199"/>
       <c r="Z11" s="29"/>
@@ -30032,19 +30103,19 @@
       <c r="AC11" s="29"/>
       <c r="AD11" s="29"/>
       <c r="AE11" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF11" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG11" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH11" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI11" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.5">
@@ -30058,42 +30129,42 @@
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F12" s="151" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="G12" s="12" t="s">
+        <v>907</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>894</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>905</v>
+      </c>
+      <c r="J12" s="15" t="s">
         <v>908</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>895</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>906</v>
-      </c>
-      <c r="J12" s="15" t="s">
-        <v>909</v>
       </c>
       <c r="K12" s="16"/>
       <c r="L12" s="17"/>
       <c r="M12" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="N12" s="25" t="s">
+        <v>882</v>
+      </c>
+      <c r="O12" s="26" t="s">
         <v>883</v>
       </c>
-      <c r="N12" s="25" t="s">
+      <c r="P12" s="27" t="s">
         <v>883</v>
       </c>
-      <c r="O12" s="26" t="s">
-        <v>884</v>
-      </c>
-      <c r="P12" s="27" t="s">
-        <v>884</v>
-      </c>
       <c r="Q12" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R12" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S12" s="24">
         <v>50</v>
@@ -30102,16 +30173,16 @@
         <v>50</v>
       </c>
       <c r="U12" s="26" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V12" s="27" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W12" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X12" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y12" s="199"/>
       <c r="Z12" s="29"/>
@@ -30120,19 +30191,19 @@
       <c r="AC12" s="29"/>
       <c r="AD12" s="29"/>
       <c r="AE12" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF12" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG12" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH12" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI12" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.5">
@@ -30146,42 +30217,42 @@
       </c>
       <c r="D13" s="23"/>
       <c r="E13" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F13" s="151" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G13" s="12" t="s">
+        <v>909</v>
+      </c>
+      <c r="H13" s="13" t="s">
         <v>910</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="I13" s="14" t="s">
         <v>911</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="J13" s="15" t="s">
         <v>912</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>913</v>
       </c>
       <c r="K13" s="16"/>
       <c r="L13" s="17"/>
       <c r="M13" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="N13" s="25" t="s">
+        <v>882</v>
+      </c>
+      <c r="O13" s="26" t="s">
         <v>883</v>
       </c>
-      <c r="N13" s="25" t="s">
+      <c r="P13" s="27" t="s">
         <v>883</v>
       </c>
-      <c r="O13" s="26" t="s">
-        <v>884</v>
-      </c>
-      <c r="P13" s="27" t="s">
-        <v>884</v>
-      </c>
       <c r="Q13" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R13" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S13" s="24">
         <v>50</v>
@@ -30190,16 +30261,16 @@
         <v>50</v>
       </c>
       <c r="U13" s="26" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V13" s="27" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W13" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X13" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y13" s="199"/>
       <c r="Z13" s="29"/>
@@ -30208,19 +30279,19 @@
       <c r="AC13" s="29"/>
       <c r="AD13" s="29"/>
       <c r="AE13" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF13" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG13" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH13" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI13" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.5">
@@ -30234,42 +30305,42 @@
       </c>
       <c r="D14" s="23"/>
       <c r="E14" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F14" s="151" t="s">
+        <v>913</v>
+      </c>
+      <c r="G14" s="12" t="s">
         <v>914</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="H14" s="13" t="s">
         <v>915</v>
       </c>
-      <c r="H14" s="13" t="s">
-        <v>916</v>
-      </c>
       <c r="I14" s="14" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="K14" s="16"/>
       <c r="L14" s="17"/>
       <c r="M14" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="N14" s="25" t="s">
+        <v>882</v>
+      </c>
+      <c r="O14" s="26" t="s">
         <v>883</v>
       </c>
-      <c r="N14" s="25" t="s">
+      <c r="P14" s="27" t="s">
         <v>883</v>
       </c>
-      <c r="O14" s="26" t="s">
-        <v>884</v>
-      </c>
-      <c r="P14" s="27" t="s">
-        <v>884</v>
-      </c>
       <c r="Q14" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R14" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S14" s="24">
         <v>50</v>
@@ -30278,16 +30349,16 @@
         <v>50</v>
       </c>
       <c r="U14" s="26" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V14" s="27" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W14" s="28" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X14" s="29" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y14" s="199"/>
       <c r="Z14" s="29"/>
@@ -30296,19 +30367,19 @@
       <c r="AC14" s="29"/>
       <c r="AD14" s="29"/>
       <c r="AE14" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF14" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG14" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH14" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI14" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
   </sheetData>
@@ -30402,7 +30473,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!G24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - VERDADERO/FALSO
+        <v>FastTest PlugIn - V8.3  - VERDADERO/FALSO
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="67" t="str">
@@ -30571,19 +30642,19 @@
       <c r="B5" s="172"/>
       <c r="D5" s="23"/>
       <c r="E5" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F5" s="76" t="s">
+        <v>916</v>
+      </c>
+      <c r="G5" s="244" t="s">
+        <v>188</v>
+      </c>
+      <c r="H5" s="25" t="s">
+        <v>882</v>
+      </c>
+      <c r="I5" s="26" t="s">
         <v>917</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="H5" s="25" t="s">
-        <v>883</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>918</v>
       </c>
       <c r="J5" s="27"/>
       <c r="K5" s="28"/>
@@ -30607,19 +30678,19 @@
       <c r="AC5" s="29"/>
       <c r="AD5" s="29"/>
       <c r="AE5" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF5" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG5" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH5" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI5" s="66" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.5">
@@ -30627,19 +30698,19 @@
       <c r="B6" s="172"/>
       <c r="D6" s="23"/>
       <c r="E6" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>919</v>
-      </c>
-      <c r="G6" s="12" t="s">
+        <v>918</v>
+      </c>
+      <c r="G6" s="244" t="s">
         <v>188</v>
       </c>
       <c r="H6" s="25" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="J6" s="27"/>
       <c r="K6" s="28"/>
@@ -30663,19 +30734,19 @@
       <c r="AC6" s="29"/>
       <c r="AD6" s="29"/>
       <c r="AE6" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF6" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG6" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI6" s="66" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.5">
@@ -30683,19 +30754,19 @@
       <c r="B7" s="172"/>
       <c r="D7" s="23"/>
       <c r="E7" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F7" s="76" t="s">
-        <v>920</v>
-      </c>
-      <c r="G7" s="12" t="s">
+        <v>919</v>
+      </c>
+      <c r="G7" s="244" t="s">
         <v>195</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="I7" s="26" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="J7" s="27"/>
       <c r="K7" s="28"/>
@@ -30719,19 +30790,19 @@
       <c r="AC7" s="29"/>
       <c r="AD7" s="29"/>
       <c r="AE7" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF7" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG7" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH7" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI7" s="66" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.5">
@@ -30739,19 +30810,19 @@
       <c r="B8" s="172"/>
       <c r="D8" s="23"/>
       <c r="E8" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F8" s="76" t="s">
-        <v>921</v>
-      </c>
-      <c r="G8" s="12" t="s">
+        <v>920</v>
+      </c>
+      <c r="G8" s="244" t="s">
         <v>195</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="J8" s="27"/>
       <c r="K8" s="28"/>
@@ -30775,19 +30846,19 @@
       <c r="AC8" s="29"/>
       <c r="AD8" s="29"/>
       <c r="AE8" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF8" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG8" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH8" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI8" s="66" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.5">
@@ -30795,19 +30866,19 @@
       <c r="B9" s="172"/>
       <c r="D9" s="23"/>
       <c r="E9" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F9" s="76" t="s">
-        <v>922</v>
-      </c>
-      <c r="G9" s="12" t="s">
+        <v>921</v>
+      </c>
+      <c r="G9" s="244" t="s">
         <v>195</v>
       </c>
       <c r="H9" s="25" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="I9" s="26" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="J9" s="27"/>
       <c r="K9" s="28"/>
@@ -30831,19 +30902,19 @@
       <c r="AC9" s="29"/>
       <c r="AD9" s="29"/>
       <c r="AE9" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF9" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG9" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH9" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI9" s="66" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.5">
@@ -30851,19 +30922,19 @@
       <c r="B10" s="172"/>
       <c r="D10" s="23"/>
       <c r="E10" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F10" s="76" t="s">
-        <v>923</v>
-      </c>
-      <c r="G10" s="12" t="s">
+        <v>922</v>
+      </c>
+      <c r="G10" s="244" t="s">
         <v>188</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="I10" s="26" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="J10" s="27"/>
       <c r="K10" s="28"/>
@@ -30887,19 +30958,19 @@
       <c r="AC10" s="29"/>
       <c r="AD10" s="29"/>
       <c r="AE10" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF10" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG10" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH10" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI10" s="66" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.5">
@@ -30907,19 +30978,19 @@
       <c r="B11" s="172"/>
       <c r="D11" s="23"/>
       <c r="E11" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F11" s="76" t="s">
-        <v>924</v>
-      </c>
-      <c r="G11" s="12" t="s">
+        <v>923</v>
+      </c>
+      <c r="G11" s="244" t="s">
         <v>188</v>
       </c>
       <c r="H11" s="25" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="I11" s="26" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="J11" s="27"/>
       <c r="K11" s="28"/>
@@ -30943,19 +31014,19 @@
       <c r="AC11" s="29"/>
       <c r="AD11" s="29"/>
       <c r="AE11" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF11" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG11" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH11" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI11" s="66" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.5">
@@ -30963,19 +31034,19 @@
       <c r="B12" s="172"/>
       <c r="D12" s="23"/>
       <c r="E12" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F12" s="76" t="s">
-        <v>925</v>
-      </c>
-      <c r="G12" s="12" t="s">
+        <v>924</v>
+      </c>
+      <c r="G12" s="244" t="s">
         <v>195</v>
       </c>
       <c r="H12" s="25" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="I12" s="26" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="J12" s="27"/>
       <c r="K12" s="28"/>
@@ -30999,19 +31070,19 @@
       <c r="AC12" s="29"/>
       <c r="AD12" s="29"/>
       <c r="AE12" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF12" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG12" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH12" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI12" s="66" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.5">
@@ -31019,19 +31090,19 @@
       <c r="B13" s="172"/>
       <c r="D13" s="23"/>
       <c r="E13" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F13" s="76" t="s">
-        <v>926</v>
-      </c>
-      <c r="G13" s="12" t="s">
+        <v>925</v>
+      </c>
+      <c r="G13" s="244" t="s">
         <v>195</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="I13" s="26" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="J13" s="27"/>
       <c r="K13" s="28"/>
@@ -31055,19 +31126,19 @@
       <c r="AC13" s="29"/>
       <c r="AD13" s="29"/>
       <c r="AE13" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF13" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG13" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH13" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI13" s="66" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.5">
@@ -31075,19 +31146,19 @@
       <c r="B14" s="172"/>
       <c r="D14" s="23"/>
       <c r="E14" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F14" s="76" t="s">
-        <v>927</v>
-      </c>
-      <c r="G14" s="12" t="s">
+        <v>926</v>
+      </c>
+      <c r="G14" s="244" t="s">
         <v>188</v>
       </c>
       <c r="H14" s="25" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="I14" s="26" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="J14" s="27"/>
       <c r="K14" s="28"/>
@@ -31111,19 +31182,19 @@
       <c r="AC14" s="29"/>
       <c r="AD14" s="29"/>
       <c r="AE14" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF14" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG14" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH14" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI14" s="66" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
   </sheetData>
@@ -31221,7 +31292,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!I24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - EMPAREJAR
+        <v>FastTest PlugIn - V8.3  - EMPAREJAR
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="103" t="str">
@@ -31456,97 +31527,97 @@
       <c r="B5" s="173"/>
       <c r="D5" s="23"/>
       <c r="E5" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F5" s="76" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G5" s="87">
         <v>2</v>
       </c>
       <c r="H5" s="87" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I5" s="88">
         <v>11</v>
       </c>
       <c r="J5" s="88" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="K5" s="89">
         <v>29</v>
       </c>
       <c r="L5" s="89" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="M5" s="90">
         <v>38</v>
       </c>
       <c r="N5" s="90" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="O5" s="91">
         <v>45</v>
       </c>
       <c r="P5" s="91" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="Q5" s="92">
         <v>58</v>
       </c>
       <c r="R5" s="92" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="S5" s="87">
         <v>66</v>
       </c>
       <c r="T5" s="87" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="U5" s="88">
         <v>72</v>
       </c>
       <c r="V5" s="88" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="W5" s="89">
         <v>86</v>
       </c>
       <c r="X5" s="89" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="Y5" s="90">
         <v>95</v>
       </c>
       <c r="Z5" s="90" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="AA5" s="91">
         <v>110</v>
       </c>
       <c r="AB5" s="91" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="AC5" s="92">
         <v>116</v>
       </c>
       <c r="AD5" s="92" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="AE5" s="30" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF5" s="31" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG5" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH5" s="33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI5" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.5">
@@ -31557,10 +31628,10 @@
       <c r="B6" s="243"/>
       <c r="D6" s="23"/>
       <c r="E6" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G6" s="87">
         <v>1</v>
@@ -31572,82 +31643,82 @@
         <v>17</v>
       </c>
       <c r="J6" s="88" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="K6" s="89">
         <v>30</v>
       </c>
       <c r="L6" s="89" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="M6" s="90">
         <v>35</v>
       </c>
       <c r="N6" s="90" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="O6" s="91">
         <v>42</v>
       </c>
       <c r="P6" s="91" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="Q6" s="92">
         <v>52</v>
       </c>
       <c r="R6" s="92" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="S6" s="87">
         <v>65</v>
       </c>
       <c r="T6" s="87" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="U6" s="88">
         <v>72</v>
       </c>
       <c r="V6" s="88" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="W6" s="89">
         <v>82</v>
       </c>
       <c r="X6" s="89" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="Y6" s="90">
         <v>98</v>
       </c>
       <c r="Z6" s="90" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="AA6" s="91">
         <v>103</v>
       </c>
       <c r="AB6" s="91" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="AC6" s="92">
         <v>120</v>
       </c>
       <c r="AD6" s="92" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="AE6" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF6" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG6" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH6" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI6" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.5">
@@ -31658,97 +31729,97 @@
       <c r="B7" s="243"/>
       <c r="D7" s="23"/>
       <c r="E7" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F7" s="76" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G7" s="87">
         <v>4</v>
       </c>
       <c r="H7" s="87" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="I7" s="88">
         <v>18</v>
       </c>
       <c r="J7" s="88" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="K7" s="89">
         <v>24</v>
       </c>
       <c r="L7" s="89" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="M7" s="90">
         <v>39</v>
       </c>
       <c r="N7" s="90" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="O7" s="91">
         <v>45</v>
       </c>
       <c r="P7" s="91" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="Q7" s="92">
         <v>56</v>
       </c>
       <c r="R7" s="92" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="S7" s="87">
         <v>68</v>
       </c>
       <c r="T7" s="87" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="U7" s="88">
         <v>79</v>
       </c>
       <c r="V7" s="88" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="W7" s="89">
         <v>85</v>
       </c>
       <c r="X7" s="89" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="Y7" s="90">
         <v>98</v>
       </c>
       <c r="Z7" s="90" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="AA7" s="91">
         <v>106</v>
       </c>
       <c r="AB7" s="91" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AC7" s="92">
         <v>115</v>
       </c>
       <c r="AD7" s="92" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="AE7" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF7" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG7" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH7" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI7" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.5">
@@ -31759,10 +31830,10 @@
       <c r="B8" s="243"/>
       <c r="D8" s="23"/>
       <c r="E8" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F8" s="76" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G8" s="87">
         <v>1</v>
@@ -31774,82 +31845,82 @@
         <v>17</v>
       </c>
       <c r="J8" s="88" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="K8" s="89">
         <v>29</v>
       </c>
       <c r="L8" s="89" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="M8" s="90">
         <v>35</v>
       </c>
       <c r="N8" s="90" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="O8" s="91">
         <v>42</v>
       </c>
       <c r="P8" s="91" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="Q8" s="92">
         <v>60</v>
       </c>
       <c r="R8" s="92" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="S8" s="87">
         <v>61</v>
       </c>
       <c r="T8" s="87" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="U8" s="88">
         <v>71</v>
       </c>
       <c r="V8" s="88" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="W8" s="89">
         <v>89</v>
       </c>
       <c r="X8" s="89" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="Y8" s="90">
         <v>91</v>
       </c>
       <c r="Z8" s="90" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="AA8" s="91">
         <v>102</v>
       </c>
       <c r="AB8" s="91" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="AC8" s="92">
         <v>119</v>
       </c>
       <c r="AD8" s="92" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="AE8" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF8" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG8" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH8" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI8" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.5">
@@ -31860,97 +31931,97 @@
       <c r="B9" s="243"/>
       <c r="D9" s="23"/>
       <c r="E9" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F9" s="76" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G9" s="87">
         <v>10</v>
       </c>
       <c r="H9" s="87" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="I9" s="88">
         <v>18</v>
       </c>
       <c r="J9" s="88" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="K9" s="89">
         <v>27</v>
       </c>
       <c r="L9" s="89" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="M9" s="90">
         <v>37</v>
       </c>
       <c r="N9" s="90" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="O9" s="91">
         <v>49</v>
       </c>
       <c r="P9" s="91" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="Q9" s="92">
         <v>51</v>
       </c>
       <c r="R9" s="92" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="S9" s="87">
         <v>69</v>
       </c>
       <c r="T9" s="87" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="U9" s="88">
         <v>72</v>
       </c>
       <c r="V9" s="88" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="W9" s="89">
         <v>85</v>
       </c>
       <c r="X9" s="89" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="Y9" s="90">
         <v>99</v>
       </c>
       <c r="Z9" s="90" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AA9" s="91">
         <v>110</v>
       </c>
       <c r="AB9" s="91" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="AC9" s="92">
         <v>114</v>
       </c>
       <c r="AD9" s="92" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="AE9" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF9" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG9" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH9" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI9" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.5">
@@ -31961,97 +32032,97 @@
       <c r="B10" s="243"/>
       <c r="D10" s="23"/>
       <c r="E10" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F10" s="76" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G10" s="87">
         <v>9</v>
       </c>
       <c r="H10" s="87" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="I10" s="88">
         <v>19</v>
       </c>
       <c r="J10" s="88" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="K10" s="89">
         <v>24</v>
       </c>
       <c r="L10" s="89" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="M10" s="90">
         <v>32</v>
       </c>
       <c r="N10" s="90" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="O10" s="91">
         <v>44</v>
       </c>
       <c r="P10" s="91" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="Q10" s="92">
         <v>52</v>
       </c>
       <c r="R10" s="92" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="S10" s="87">
         <v>67</v>
       </c>
       <c r="T10" s="87" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="U10" s="88">
         <v>75</v>
       </c>
       <c r="V10" s="88" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="W10" s="89">
         <v>83</v>
       </c>
       <c r="X10" s="89" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="Y10" s="90">
         <v>95</v>
       </c>
       <c r="Z10" s="90" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="AA10" s="91">
         <v>109</v>
       </c>
       <c r="AB10" s="91" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="AC10" s="92">
         <v>112</v>
       </c>
       <c r="AD10" s="92" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="AE10" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF10" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG10" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH10" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI10" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.5">
@@ -32062,97 +32133,97 @@
       <c r="B11" s="243"/>
       <c r="D11" s="23"/>
       <c r="E11" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F11" s="76" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G11" s="87">
         <v>3</v>
       </c>
       <c r="H11" s="87" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="I11" s="88">
         <v>11</v>
       </c>
       <c r="J11" s="88" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="K11" s="89">
         <v>30</v>
       </c>
       <c r="L11" s="89" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="M11" s="90">
         <v>35</v>
       </c>
       <c r="N11" s="90" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="O11" s="91">
         <v>42</v>
       </c>
       <c r="P11" s="91" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="Q11" s="92">
         <v>53</v>
       </c>
       <c r="R11" s="92" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="S11" s="87">
         <v>66</v>
       </c>
       <c r="T11" s="87" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="U11" s="88">
         <v>74</v>
       </c>
       <c r="V11" s="88" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="W11" s="89">
         <v>89</v>
       </c>
       <c r="X11" s="89" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="Y11" s="90">
         <v>96</v>
       </c>
       <c r="Z11" s="90" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="AA11" s="91">
         <v>110</v>
       </c>
       <c r="AB11" s="91" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="AC11" s="92">
         <v>113</v>
       </c>
       <c r="AD11" s="92" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="AE11" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF11" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG11" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH11" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI11" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.5">
@@ -32163,97 +32234,97 @@
       <c r="B12" s="243"/>
       <c r="D12" s="23"/>
       <c r="E12" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F12" s="76" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G12" s="87">
         <v>9</v>
       </c>
       <c r="H12" s="87" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="I12" s="88">
         <v>12</v>
       </c>
       <c r="J12" s="88" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K12" s="89">
         <v>27</v>
       </c>
       <c r="L12" s="89" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="M12" s="90">
         <v>31</v>
       </c>
       <c r="N12" s="90" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O12" s="91">
         <v>43</v>
       </c>
       <c r="P12" s="91" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="Q12" s="92">
         <v>54</v>
       </c>
       <c r="R12" s="92" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="S12" s="87">
         <v>61</v>
       </c>
       <c r="T12" s="87" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="U12" s="88">
         <v>75</v>
       </c>
       <c r="V12" s="88" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="W12" s="89">
         <v>82</v>
       </c>
       <c r="X12" s="89" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="Y12" s="90">
         <v>98</v>
       </c>
       <c r="Z12" s="90" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="AA12" s="91">
         <v>108</v>
       </c>
       <c r="AB12" s="91" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="AC12" s="92">
         <v>112</v>
       </c>
       <c r="AD12" s="92" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="AE12" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF12" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG12" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH12" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI12" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.5">
@@ -32264,97 +32335,97 @@
       <c r="B13" s="243"/>
       <c r="D13" s="23"/>
       <c r="E13" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F13" s="76" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G13" s="87">
         <v>9</v>
       </c>
       <c r="H13" s="87" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="I13" s="88">
         <v>16</v>
       </c>
       <c r="J13" s="88" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="K13" s="89">
         <v>25</v>
       </c>
       <c r="L13" s="89" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="M13" s="90">
         <v>32</v>
       </c>
       <c r="N13" s="90" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="O13" s="91">
         <v>44</v>
       </c>
       <c r="P13" s="91" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="Q13" s="92">
         <v>58</v>
       </c>
       <c r="R13" s="92" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="S13" s="87">
         <v>70</v>
       </c>
       <c r="T13" s="87" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="U13" s="88">
         <v>74</v>
       </c>
       <c r="V13" s="88" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="W13" s="89">
         <v>88</v>
       </c>
       <c r="X13" s="89" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="Y13" s="90">
         <v>97</v>
       </c>
       <c r="Z13" s="90" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="AA13" s="91">
         <v>101</v>
       </c>
       <c r="AB13" s="91" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="AC13" s="92">
         <v>112</v>
       </c>
       <c r="AD13" s="92" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="AE13" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF13" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG13" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH13" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI13" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.5">
@@ -32365,97 +32436,97 @@
       <c r="B14" s="243"/>
       <c r="D14" s="23"/>
       <c r="E14" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F14" s="76" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G14" s="87">
         <v>3</v>
       </c>
       <c r="H14" s="87" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="I14" s="88">
         <v>15</v>
       </c>
       <c r="J14" s="88" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="K14" s="89">
         <v>24</v>
       </c>
       <c r="L14" s="89" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="M14" s="90">
         <v>40</v>
       </c>
       <c r="N14" s="90" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="O14" s="91">
         <v>44</v>
       </c>
       <c r="P14" s="91" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="Q14" s="92">
         <v>59</v>
       </c>
       <c r="R14" s="92" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="S14" s="87">
         <v>69</v>
       </c>
       <c r="T14" s="87" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="U14" s="88">
         <v>71</v>
       </c>
       <c r="V14" s="88" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="W14" s="89">
         <v>83</v>
       </c>
       <c r="X14" s="89" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="Y14" s="90">
         <v>93</v>
       </c>
       <c r="Z14" s="90" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="AA14" s="91">
         <v>110</v>
       </c>
       <c r="AB14" s="91" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="AC14" s="92">
         <v>115</v>
       </c>
       <c r="AD14" s="92" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="AE14" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF14" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG14" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH14" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI14" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
   </sheetData>
@@ -32562,7 +32633,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!K24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - RESPUESTA CORTA
+        <v>FastTest PlugIn - V8.3  - RESPUESTA CORTA
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="103" t="str">
@@ -32801,97 +32872,97 @@
         <v>0</v>
       </c>
       <c r="E5" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F5" s="76" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="G5" s="87" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H5" s="98">
         <v>100</v>
       </c>
       <c r="I5" s="98" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J5" s="88" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="K5" s="99">
         <v>100</v>
       </c>
       <c r="L5" s="99" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="M5" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="N5" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O5" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="P5" s="90" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Q5" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R5" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S5" s="91" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="T5" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="U5" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V5" s="92" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W5" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X5" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y5" s="87" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z5" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA5" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB5" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC5" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD5" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE5" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF5" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG5" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH5" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI5" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.5">
@@ -32906,97 +32977,97 @@
         <v>0</v>
       </c>
       <c r="E6" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F6" s="76" t="s">
+        <v>974</v>
+      </c>
+      <c r="G6" s="87" t="s">
         <v>975</v>
-      </c>
-      <c r="G6" s="87" t="s">
-        <v>976</v>
       </c>
       <c r="H6" s="98">
         <v>100</v>
       </c>
       <c r="I6" s="98" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J6" s="88" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="K6" s="99">
         <v>100</v>
       </c>
       <c r="L6" s="99" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="M6" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="N6" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O6" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="P6" s="90" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Q6" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R6" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S6" s="91" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="T6" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="U6" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V6" s="92" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W6" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X6" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y6" s="87" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z6" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA6" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB6" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC6" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD6" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE6" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF6" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG6" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH6" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI6" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.5">
@@ -33011,97 +33082,97 @@
         <v>0</v>
       </c>
       <c r="E7" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F7" s="76" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G7" s="87" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H7" s="98">
         <v>100</v>
       </c>
       <c r="I7" s="98" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J7" s="88" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="K7" s="99">
         <v>100</v>
       </c>
       <c r="L7" s="99" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="M7" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="N7" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O7" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="P7" s="90" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Q7" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R7" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S7" s="91" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="T7" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="U7" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V7" s="92" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W7" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X7" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y7" s="87" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z7" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA7" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB7" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC7" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD7" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE7" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF7" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG7" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH7" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI7" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.5">
@@ -33116,97 +33187,97 @@
         <v>0</v>
       </c>
       <c r="E8" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F8" s="76" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="G8" s="87" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H8" s="98">
         <v>100</v>
       </c>
       <c r="I8" s="98" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J8" s="88" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="K8" s="99">
         <v>100</v>
       </c>
       <c r="L8" s="99" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="M8" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="N8" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O8" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="P8" s="90" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Q8" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R8" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S8" s="91" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="T8" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="U8" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V8" s="92" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W8" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X8" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y8" s="87" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z8" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA8" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB8" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC8" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD8" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE8" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF8" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG8" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH8" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI8" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.5">
@@ -33221,97 +33292,97 @@
         <v>0</v>
       </c>
       <c r="E9" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F9" s="76" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="G9" s="87" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H9" s="98">
         <v>100</v>
       </c>
       <c r="I9" s="98" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J9" s="88" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="K9" s="99">
         <v>100</v>
       </c>
       <c r="L9" s="99" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="M9" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="N9" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O9" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="P9" s="90" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Q9" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R9" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S9" s="91" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="T9" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="U9" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V9" s="92" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W9" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X9" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y9" s="87" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z9" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA9" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB9" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC9" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD9" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE9" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF9" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG9" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH9" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI9" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.5">
@@ -33326,97 +33397,97 @@
         <v>0</v>
       </c>
       <c r="E10" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F10" s="76" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="G10" s="87" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H10" s="98">
         <v>100</v>
       </c>
       <c r="I10" s="98" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J10" s="88" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="K10" s="99">
         <v>100</v>
       </c>
       <c r="L10" s="99" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="M10" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="N10" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O10" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="P10" s="90" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Q10" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R10" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S10" s="91" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="T10" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="U10" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V10" s="92" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W10" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X10" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y10" s="87" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z10" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA10" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB10" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC10" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD10" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE10" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF10" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG10" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH10" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI10" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.5">
@@ -33431,97 +33502,97 @@
         <v>0</v>
       </c>
       <c r="E11" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F11" s="76" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="G11" s="87" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H11" s="98">
         <v>100</v>
       </c>
       <c r="I11" s="98" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J11" s="88" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="K11" s="99">
         <v>100</v>
       </c>
       <c r="L11" s="99" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="M11" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="N11" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O11" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="P11" s="90" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Q11" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R11" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S11" s="91" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="T11" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="U11" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V11" s="92" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W11" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X11" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y11" s="87" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z11" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA11" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB11" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC11" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD11" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE11" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF11" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG11" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH11" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI11" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.5">
@@ -33536,97 +33607,97 @@
         <v>0</v>
       </c>
       <c r="E12" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F12" s="76" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G12" s="87" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H12" s="98">
         <v>100</v>
       </c>
       <c r="I12" s="98" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J12" s="88" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="K12" s="99">
         <v>100</v>
       </c>
       <c r="L12" s="99" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="M12" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="N12" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O12" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="P12" s="90" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Q12" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R12" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S12" s="91" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="T12" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="U12" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V12" s="92" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W12" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X12" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y12" s="87" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z12" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA12" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB12" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC12" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD12" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE12" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF12" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG12" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH12" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI12" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.5">
@@ -33641,97 +33712,97 @@
         <v>0</v>
       </c>
       <c r="E13" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F13" s="76" t="s">
+        <v>989</v>
+      </c>
+      <c r="G13" s="87" t="s">
         <v>990</v>
-      </c>
-      <c r="G13" s="87" t="s">
-        <v>991</v>
       </c>
       <c r="H13" s="98">
         <v>100</v>
       </c>
       <c r="I13" s="98" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J13" s="88" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="K13" s="99">
         <v>100</v>
       </c>
       <c r="L13" s="99" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="M13" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="N13" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O13" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="P13" s="90" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Q13" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R13" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S13" s="91" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="T13" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="U13" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V13" s="92" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W13" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X13" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y13" s="87" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z13" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA13" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB13" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC13" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD13" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE13" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF13" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG13" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH13" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI13" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.5">
@@ -33746,97 +33817,97 @@
         <v>0</v>
       </c>
       <c r="E14" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F14" s="76" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="G14" s="87" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H14" s="98">
         <v>100</v>
       </c>
       <c r="I14" s="98" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J14" s="88" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="K14" s="99">
         <v>100</v>
       </c>
       <c r="L14" s="99" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="M14" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="N14" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O14" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="P14" s="90" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Q14" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R14" s="100" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="S14" s="91" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="T14" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="U14" s="101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="V14" s="92" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W14" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X14" s="102" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y14" s="87" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z14" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA14" s="98" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB14" s="88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC14" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD14" s="99" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE14" s="93" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF14" s="94" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG14" s="95" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH14" s="96" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI14" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
   </sheetData>
@@ -33934,7 +34005,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!M24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - PALABRA PERDIDA
+        <v>FastTest PlugIn - V8.3  - PALABRA PERDIDA
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="117" t="str">
@@ -34194,10 +34265,10 @@
       <c r="C5" s="152"/>
       <c r="D5" s="152"/>
       <c r="E5" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F5" s="151" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="G5" s="12">
         <v>1</v>
@@ -34227,64 +34298,64 @@
         <v>2</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="Q5" s="13">
         <v>2</v>
       </c>
       <c r="R5" s="13" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="S5" s="12">
         <v>2</v>
       </c>
       <c r="T5" s="12" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="U5" s="13">
         <v>2</v>
       </c>
       <c r="V5" s="13" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="W5" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X5" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y5" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z5" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA5" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB5" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC5" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD5" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE5" s="153" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF5" s="154" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG5" s="155" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH5" s="156" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI5" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.5">
@@ -34296,10 +34367,10 @@
       <c r="C6" s="152"/>
       <c r="D6" s="152"/>
       <c r="E6" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F6" s="151" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="G6" s="12">
         <v>1</v>
@@ -34329,64 +34400,64 @@
         <v>2</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="Q6" s="13">
         <v>2</v>
       </c>
       <c r="R6" s="13" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="S6" s="12">
         <v>2</v>
       </c>
       <c r="T6" s="12" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="U6" s="13">
         <v>2</v>
       </c>
       <c r="V6" s="13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="W6" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X6" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y6" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z6" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA6" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB6" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC6" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD6" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE6" s="153" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF6" s="154" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG6" s="155" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH6" s="156" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI6" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.5">
@@ -34398,10 +34469,10 @@
       <c r="C7" s="152"/>
       <c r="D7" s="152"/>
       <c r="E7" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F7" s="151" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="G7" s="12">
         <v>1</v>
@@ -34431,64 +34502,64 @@
         <v>2</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="Q7" s="13">
         <v>2</v>
       </c>
       <c r="R7" s="13" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="S7" s="12">
         <v>2</v>
       </c>
       <c r="T7" s="12" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="U7" s="13">
         <v>2</v>
       </c>
       <c r="V7" s="13" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="W7" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X7" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y7" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z7" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA7" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB7" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC7" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD7" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE7" s="153" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF7" s="154" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG7" s="155" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH7" s="156" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI7" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.5">
@@ -34500,10 +34571,10 @@
       <c r="C8" s="152"/>
       <c r="D8" s="152"/>
       <c r="E8" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F8" s="151" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G8" s="12">
         <v>1</v>
@@ -34533,64 +34604,64 @@
         <v>2</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="Q8" s="13">
         <v>2</v>
       </c>
       <c r="R8" s="13" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="S8" s="12">
         <v>2</v>
       </c>
       <c r="T8" s="12" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="U8" s="13">
         <v>2</v>
       </c>
       <c r="V8" s="13" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="W8" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X8" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y8" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z8" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA8" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB8" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC8" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD8" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE8" s="153" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF8" s="154" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG8" s="155" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH8" s="156" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI8" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.5">
@@ -34602,10 +34673,10 @@
       <c r="C9" s="152"/>
       <c r="D9" s="152"/>
       <c r="E9" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F9" s="151" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="G9" s="12">
         <v>1</v>
@@ -34635,64 +34706,64 @@
         <v>2</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="Q9" s="13">
         <v>2</v>
       </c>
       <c r="R9" s="13" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="S9" s="12">
         <v>2</v>
       </c>
       <c r="T9" s="12" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="U9" s="13">
         <v>2</v>
       </c>
       <c r="V9" s="13" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="W9" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X9" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y9" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z9" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA9" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB9" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC9" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD9" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE9" s="153" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF9" s="154" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG9" s="155" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH9" s="156" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI9" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.5">
@@ -34704,10 +34775,10 @@
       <c r="C10" s="152"/>
       <c r="D10" s="152"/>
       <c r="E10" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F10" s="151" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G10" s="12">
         <v>1</v>
@@ -34737,64 +34808,64 @@
         <v>2</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="Q10" s="13">
         <v>2</v>
       </c>
       <c r="R10" s="13" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="S10" s="12">
         <v>2</v>
       </c>
       <c r="T10" s="12" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="U10" s="13">
         <v>2</v>
       </c>
       <c r="V10" s="13" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="W10" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X10" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y10" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z10" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA10" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB10" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC10" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD10" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE10" s="153" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF10" s="154" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG10" s="155" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH10" s="156" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI10" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.5">
@@ -34806,10 +34877,10 @@
       <c r="C11" s="152"/>
       <c r="D11" s="152"/>
       <c r="E11" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F11" s="151" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="G11" s="12">
         <v>1</v>
@@ -34839,64 +34910,64 @@
         <v>2</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="Q11" s="13">
         <v>2</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="S11" s="12">
         <v>2</v>
       </c>
       <c r="T11" s="12" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="U11" s="13">
         <v>2</v>
       </c>
       <c r="V11" s="13" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="W11" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X11" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y11" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z11" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA11" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB11" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC11" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD11" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE11" s="153" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF11" s="154" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG11" s="155" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH11" s="156" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI11" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.5">
@@ -34908,10 +34979,10 @@
       <c r="C12" s="152"/>
       <c r="D12" s="152"/>
       <c r="E12" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F12" s="151" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="G12" s="12">
         <v>1</v>
@@ -34947,58 +35018,58 @@
         <v>2</v>
       </c>
       <c r="R12" s="13" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="S12" s="12">
         <v>2</v>
       </c>
       <c r="T12" s="12" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="U12" s="13">
         <v>2</v>
       </c>
       <c r="V12" s="13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="W12" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X12" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y12" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z12" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA12" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB12" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC12" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD12" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE12" s="153" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF12" s="154" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG12" s="155" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH12" s="156" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI12" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.5">
@@ -35010,10 +35081,10 @@
       <c r="C13" s="152"/>
       <c r="D13" s="152"/>
       <c r="E13" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F13" s="151" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G13" s="12">
         <v>1</v>
@@ -35043,64 +35114,64 @@
         <v>2</v>
       </c>
       <c r="P13" s="12" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="Q13" s="13">
         <v>2</v>
       </c>
       <c r="R13" s="13" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="S13" s="12">
         <v>2</v>
       </c>
       <c r="T13" s="12" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="U13" s="13">
         <v>2</v>
       </c>
       <c r="V13" s="13" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="W13" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X13" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y13" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z13" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA13" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB13" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC13" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD13" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE13" s="153" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF13" s="154" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG13" s="155" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH13" s="156" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI13" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.5">
@@ -35112,10 +35183,10 @@
       <c r="C14" s="152"/>
       <c r="D14" s="152"/>
       <c r="E14" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F14" s="151" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="G14" s="12">
         <v>1</v>
@@ -35145,64 +35216,64 @@
         <v>2</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="Q14" s="13">
         <v>2</v>
       </c>
       <c r="R14" s="13" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="S14" s="12">
         <v>2</v>
       </c>
       <c r="T14" s="12" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="U14" s="13">
         <v>2</v>
       </c>
       <c r="V14" s="13" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="W14" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="X14" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Y14" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Z14" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA14" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AB14" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AC14" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD14" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AE14" s="153" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF14" s="154" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG14" s="155" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH14" s="156" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI14" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
   </sheetData>
@@ -35303,7 +35374,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!O24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - ENSAYO
+        <v>FastTest PlugIn - V8.3  - ENSAYO
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="55" t="str">
@@ -35475,16 +35546,16 @@
       <c r="C5" s="152"/>
       <c r="D5" s="152"/>
       <c r="E5" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F5" s="151" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G5" s="128" t="s">
         <v>1008</v>
       </c>
-      <c r="G5" s="128" t="s">
+      <c r="H5" s="25" t="s">
         <v>1009</v>
-      </c>
-      <c r="H5" s="25" t="s">
-        <v>1010</v>
       </c>
       <c r="I5" s="14">
         <v>10</v>
@@ -35493,16 +35564,16 @@
         <v>2</v>
       </c>
       <c r="K5" s="130" t="s">
+        <v>1010</v>
+      </c>
+      <c r="L5" s="131" t="s">
         <v>1011</v>
       </c>
-      <c r="L5" s="131" t="s">
+      <c r="M5" s="128" t="s">
         <v>1012</v>
       </c>
-      <c r="M5" s="128" t="s">
-        <v>1013</v>
-      </c>
       <c r="N5" s="157" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O5" s="158"/>
       <c r="P5" s="158"/>
@@ -35525,7 +35596,7 @@
       <c r="AG5" s="161"/>
       <c r="AH5" s="162"/>
       <c r="AI5" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="6" spans="1:35" ht="23.35" x14ac:dyDescent="0.5">
@@ -35534,16 +35605,16 @@
       <c r="C6" s="152"/>
       <c r="D6" s="152"/>
       <c r="E6" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F6" s="151" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="G6" s="128" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H6" s="25" t="s">
         <v>1009</v>
-      </c>
-      <c r="H6" s="25" t="s">
-        <v>1010</v>
       </c>
       <c r="I6" s="14">
         <v>10</v>
@@ -35552,16 +35623,16 @@
         <v>2</v>
       </c>
       <c r="K6" s="130" t="s">
+        <v>1010</v>
+      </c>
+      <c r="L6" s="131" t="s">
         <v>1011</v>
       </c>
-      <c r="L6" s="131" t="s">
+      <c r="M6" s="128" t="s">
         <v>1012</v>
       </c>
-      <c r="M6" s="128" t="s">
-        <v>1013</v>
-      </c>
       <c r="N6" s="157" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O6" s="158"/>
       <c r="P6" s="158"/>
@@ -35584,7 +35655,7 @@
       <c r="AG6" s="161"/>
       <c r="AH6" s="162"/>
       <c r="AI6" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="23.35" x14ac:dyDescent="0.5">
@@ -35593,16 +35664,16 @@
       <c r="C7" s="152"/>
       <c r="D7" s="152"/>
       <c r="E7" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F7" s="151" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="G7" s="128" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H7" s="25" t="s">
         <v>1009</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>1010</v>
       </c>
       <c r="I7" s="14">
         <v>10</v>
@@ -35611,16 +35682,16 @@
         <v>2</v>
       </c>
       <c r="K7" s="130" t="s">
+        <v>1010</v>
+      </c>
+      <c r="L7" s="131" t="s">
         <v>1011</v>
       </c>
-      <c r="L7" s="131" t="s">
+      <c r="M7" s="128" t="s">
         <v>1012</v>
       </c>
-      <c r="M7" s="128" t="s">
-        <v>1013</v>
-      </c>
       <c r="N7" s="157" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O7" s="158"/>
       <c r="P7" s="158"/>
@@ -35643,7 +35714,7 @@
       <c r="AG7" s="161"/>
       <c r="AH7" s="162"/>
       <c r="AI7" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="8" spans="1:35" ht="23.35" x14ac:dyDescent="0.5">
@@ -35652,16 +35723,16 @@
       <c r="C8" s="152"/>
       <c r="D8" s="152"/>
       <c r="E8" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F8" s="151" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="G8" s="128" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H8" s="25" t="s">
         <v>1009</v>
-      </c>
-      <c r="H8" s="25" t="s">
-        <v>1010</v>
       </c>
       <c r="I8" s="14">
         <v>10</v>
@@ -35670,16 +35741,16 @@
         <v>2</v>
       </c>
       <c r="K8" s="130" t="s">
+        <v>1010</v>
+      </c>
+      <c r="L8" s="131" t="s">
         <v>1011</v>
       </c>
-      <c r="L8" s="131" t="s">
+      <c r="M8" s="128" t="s">
         <v>1012</v>
       </c>
-      <c r="M8" s="128" t="s">
-        <v>1013</v>
-      </c>
       <c r="N8" s="157" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O8" s="158"/>
       <c r="P8" s="158"/>
@@ -35702,7 +35773,7 @@
       <c r="AG8" s="161"/>
       <c r="AH8" s="162"/>
       <c r="AI8" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="9" spans="1:35" ht="23.35" x14ac:dyDescent="0.5">
@@ -35711,16 +35782,16 @@
       <c r="C9" s="152"/>
       <c r="D9" s="152"/>
       <c r="E9" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F9" s="151" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="G9" s="128" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H9" s="25" t="s">
         <v>1009</v>
-      </c>
-      <c r="H9" s="25" t="s">
-        <v>1010</v>
       </c>
       <c r="I9" s="14">
         <v>10</v>
@@ -35729,16 +35800,16 @@
         <v>2</v>
       </c>
       <c r="K9" s="130" t="s">
+        <v>1010</v>
+      </c>
+      <c r="L9" s="131" t="s">
         <v>1011</v>
       </c>
-      <c r="L9" s="131" t="s">
+      <c r="M9" s="128" t="s">
         <v>1012</v>
       </c>
-      <c r="M9" s="128" t="s">
-        <v>1013</v>
-      </c>
       <c r="N9" s="157" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O9" s="158"/>
       <c r="P9" s="158"/>
@@ -35761,7 +35832,7 @@
       <c r="AG9" s="161"/>
       <c r="AH9" s="162"/>
       <c r="AI9" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="10" spans="1:35" ht="23.35" x14ac:dyDescent="0.5">
@@ -35770,16 +35841,16 @@
       <c r="C10" s="152"/>
       <c r="D10" s="152"/>
       <c r="E10" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F10" s="151" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G10" s="128" t="s">
         <v>1008</v>
       </c>
-      <c r="G10" s="128" t="s">
+      <c r="H10" s="25" t="s">
         <v>1009</v>
-      </c>
-      <c r="H10" s="25" t="s">
-        <v>1010</v>
       </c>
       <c r="I10" s="14">
         <v>10</v>
@@ -35788,16 +35859,16 @@
         <v>2</v>
       </c>
       <c r="K10" s="130" t="s">
+        <v>1010</v>
+      </c>
+      <c r="L10" s="131" t="s">
         <v>1011</v>
       </c>
-      <c r="L10" s="131" t="s">
+      <c r="M10" s="128" t="s">
         <v>1012</v>
       </c>
-      <c r="M10" s="128" t="s">
-        <v>1013</v>
-      </c>
       <c r="N10" s="157" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O10" s="158"/>
       <c r="P10" s="158"/>
@@ -35820,7 +35891,7 @@
       <c r="AG10" s="161"/>
       <c r="AH10" s="162"/>
       <c r="AI10" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="11" spans="1:35" ht="23.35" x14ac:dyDescent="0.5">
@@ -35829,16 +35900,16 @@
       <c r="C11" s="152"/>
       <c r="D11" s="152"/>
       <c r="E11" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F11" s="151" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G11" s="128" t="s">
         <v>1008</v>
       </c>
-      <c r="G11" s="128" t="s">
+      <c r="H11" s="25" t="s">
         <v>1009</v>
-      </c>
-      <c r="H11" s="25" t="s">
-        <v>1010</v>
       </c>
       <c r="I11" s="14">
         <v>10</v>
@@ -35847,16 +35918,16 @@
         <v>2</v>
       </c>
       <c r="K11" s="130" t="s">
+        <v>1010</v>
+      </c>
+      <c r="L11" s="131" t="s">
         <v>1011</v>
       </c>
-      <c r="L11" s="131" t="s">
+      <c r="M11" s="128" t="s">
         <v>1012</v>
       </c>
-      <c r="M11" s="128" t="s">
-        <v>1013</v>
-      </c>
       <c r="N11" s="157" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O11" s="158"/>
       <c r="P11" s="158"/>
@@ -35879,7 +35950,7 @@
       <c r="AG11" s="161"/>
       <c r="AH11" s="162"/>
       <c r="AI11" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="12" spans="1:35" ht="23.35" x14ac:dyDescent="0.5">
@@ -35888,16 +35959,16 @@
       <c r="C12" s="152"/>
       <c r="D12" s="152"/>
       <c r="E12" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F12" s="151" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="G12" s="128" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H12" s="25" t="s">
         <v>1009</v>
-      </c>
-      <c r="H12" s="25" t="s">
-        <v>1010</v>
       </c>
       <c r="I12" s="14">
         <v>10</v>
@@ -35906,16 +35977,16 @@
         <v>2</v>
       </c>
       <c r="K12" s="130" t="s">
+        <v>1010</v>
+      </c>
+      <c r="L12" s="131" t="s">
         <v>1011</v>
       </c>
-      <c r="L12" s="131" t="s">
+      <c r="M12" s="128" t="s">
         <v>1012</v>
       </c>
-      <c r="M12" s="128" t="s">
-        <v>1013</v>
-      </c>
       <c r="N12" s="157" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O12" s="158"/>
       <c r="P12" s="158"/>
@@ -35938,7 +36009,7 @@
       <c r="AG12" s="161"/>
       <c r="AH12" s="162"/>
       <c r="AI12" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="13" spans="1:35" ht="23.35" x14ac:dyDescent="0.5">
@@ -35947,16 +36018,16 @@
       <c r="C13" s="152"/>
       <c r="D13" s="152"/>
       <c r="E13" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F13" s="151" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G13" s="128" t="s">
         <v>1008</v>
       </c>
-      <c r="G13" s="128" t="s">
+      <c r="H13" s="25" t="s">
         <v>1009</v>
-      </c>
-      <c r="H13" s="25" t="s">
-        <v>1010</v>
       </c>
       <c r="I13" s="14">
         <v>10</v>
@@ -35965,16 +36036,16 @@
         <v>2</v>
       </c>
       <c r="K13" s="130" t="s">
+        <v>1010</v>
+      </c>
+      <c r="L13" s="131" t="s">
         <v>1011</v>
       </c>
-      <c r="L13" s="131" t="s">
+      <c r="M13" s="128" t="s">
         <v>1012</v>
       </c>
-      <c r="M13" s="128" t="s">
-        <v>1013</v>
-      </c>
       <c r="N13" s="157" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O13" s="158"/>
       <c r="P13" s="158"/>
@@ -35997,7 +36068,7 @@
       <c r="AG13" s="161"/>
       <c r="AH13" s="162"/>
       <c r="AI13" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="14" spans="1:35" ht="23.35" x14ac:dyDescent="0.5">
@@ -36006,16 +36077,16 @@
       <c r="C14" s="152"/>
       <c r="D14" s="152"/>
       <c r="E14" s="119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F14" s="151" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="G14" s="128" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H14" s="25" t="s">
         <v>1009</v>
-      </c>
-      <c r="H14" s="25" t="s">
-        <v>1010</v>
       </c>
       <c r="I14" s="14">
         <v>10</v>
@@ -36024,16 +36095,16 @@
         <v>2</v>
       </c>
       <c r="K14" s="130" t="s">
+        <v>1010</v>
+      </c>
+      <c r="L14" s="131" t="s">
         <v>1011</v>
       </c>
-      <c r="L14" s="131" t="s">
+      <c r="M14" s="128" t="s">
         <v>1012</v>
       </c>
-      <c r="M14" s="128" t="s">
-        <v>1013</v>
-      </c>
       <c r="N14" s="157" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O14" s="158"/>
       <c r="P14" s="158"/>
@@ -36056,16 +36127,16 @@
       <c r="AG14" s="161"/>
       <c r="AH14" s="162"/>
       <c r="AI14" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="eiKFE7U7iu3v3NIXz0Uoww9HthhK7LfIiktbt/wKm8OBOuEgD3LzDp3lbtp0B8o6LebNBLHj5ne1BduUntV/Wg==" saltValue="j2iU3ZojPc5WkJ68bmzvVQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <conditionalFormatting sqref="G5:K14">
-    <cfRule type="cellIs" dxfId="119" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36148,8 +36219,8 @@
       </c>
     </row>
     <row r="3" spans="1:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="276"/>
-      <c r="B3" s="276"/>
+      <c r="A3" s="277"/>
+      <c r="B3" s="277"/>
       <c r="C3" s="18"/>
       <c r="D3" s="18"/>
       <c r="E3" s="22" t="str">
@@ -36159,7 +36230,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!Q24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - CLOZE
+        <v>FastTest PlugIn - V8.3  - CLOZE
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="133" t="str">
@@ -36320,16 +36391,16 @@
         <v>279</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="58.35" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:35" ht="93.35" x14ac:dyDescent="0.5">
       <c r="A5" s="175"/>
       <c r="B5" s="176"/>
       <c r="C5" s="152"/>
       <c r="D5" s="152"/>
       <c r="E5" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F5" s="151" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="G5" s="163">
         <v>10</v>
@@ -36358,19 +36429,19 @@
       <c r="AC5" s="157"/>
       <c r="AD5" s="157"/>
       <c r="AE5" s="164" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF5" s="165" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG5" s="166" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH5" s="167" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI5" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="6" spans="1:35" ht="58.35" x14ac:dyDescent="0.5">
@@ -36379,10 +36450,10 @@
       <c r="C6" s="152"/>
       <c r="D6" s="152"/>
       <c r="E6" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F6" s="151" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G6" s="163">
         <v>10</v>
@@ -36411,19 +36482,19 @@
       <c r="AC6" s="157"/>
       <c r="AD6" s="157"/>
       <c r="AE6" s="164" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF6" s="165" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG6" s="166" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH6" s="167" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI6" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="58.35" x14ac:dyDescent="0.5">
@@ -36432,10 +36503,10 @@
       <c r="C7" s="152"/>
       <c r="D7" s="152"/>
       <c r="E7" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F7" s="151" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="G7" s="163">
         <v>10</v>
@@ -36464,19 +36535,19 @@
       <c r="AC7" s="157"/>
       <c r="AD7" s="157"/>
       <c r="AE7" s="164" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF7" s="165" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG7" s="166" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH7" s="167" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI7" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="8" spans="1:35" ht="58.35" x14ac:dyDescent="0.5">
@@ -36485,10 +36556,10 @@
       <c r="C8" s="152"/>
       <c r="D8" s="152"/>
       <c r="E8" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F8" s="151" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="G8" s="163">
         <v>10</v>
@@ -36517,19 +36588,19 @@
       <c r="AC8" s="157"/>
       <c r="AD8" s="157"/>
       <c r="AE8" s="164" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF8" s="165" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG8" s="166" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH8" s="167" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI8" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="9" spans="1:35" ht="58.35" x14ac:dyDescent="0.5">
@@ -36538,10 +36609,10 @@
       <c r="C9" s="152"/>
       <c r="D9" s="152"/>
       <c r="E9" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F9" s="151" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="G9" s="163">
         <v>10</v>
@@ -36570,19 +36641,19 @@
       <c r="AC9" s="157"/>
       <c r="AD9" s="157"/>
       <c r="AE9" s="164" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF9" s="165" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG9" s="166" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH9" s="167" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI9" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="10" spans="1:35" ht="58.35" x14ac:dyDescent="0.5">
@@ -36591,10 +36662,10 @@
       <c r="C10" s="152"/>
       <c r="D10" s="152"/>
       <c r="E10" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F10" s="151" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="G10" s="163">
         <v>10</v>
@@ -36623,19 +36694,19 @@
       <c r="AC10" s="157"/>
       <c r="AD10" s="157"/>
       <c r="AE10" s="164" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF10" s="165" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG10" s="166" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH10" s="167" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI10" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="11" spans="1:35" ht="58.35" x14ac:dyDescent="0.5">
@@ -36644,10 +36715,10 @@
       <c r="C11" s="152"/>
       <c r="D11" s="152"/>
       <c r="E11" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F11" s="151" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="G11" s="163">
         <v>10</v>
@@ -36676,19 +36747,19 @@
       <c r="AC11" s="157"/>
       <c r="AD11" s="157"/>
       <c r="AE11" s="164" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF11" s="165" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG11" s="166" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH11" s="167" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI11" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="12" spans="1:35" ht="58.35" x14ac:dyDescent="0.5">
@@ -36697,10 +36768,10 @@
       <c r="C12" s="152"/>
       <c r="D12" s="152"/>
       <c r="E12" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F12" s="151" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
       <c r="G12" s="163">
         <v>10</v>
@@ -36729,19 +36800,19 @@
       <c r="AC12" s="157"/>
       <c r="AD12" s="157"/>
       <c r="AE12" s="164" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF12" s="165" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG12" s="166" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH12" s="167" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI12" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="13" spans="1:35" ht="58.35" x14ac:dyDescent="0.5">
@@ -36750,10 +36821,10 @@
       <c r="C13" s="152"/>
       <c r="D13" s="152"/>
       <c r="E13" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F13" s="151" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="G13" s="163">
         <v>10</v>
@@ -36782,19 +36853,19 @@
       <c r="AC13" s="157"/>
       <c r="AD13" s="157"/>
       <c r="AE13" s="164" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF13" s="165" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG13" s="166" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH13" s="167" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI13" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="14" spans="1:35" ht="58.35" x14ac:dyDescent="0.5">
@@ -36803,10 +36874,10 @@
       <c r="C14" s="152"/>
       <c r="D14" s="152"/>
       <c r="E14" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F14" s="151" t="s">
-        <v>1018</v>
+        <v>1027</v>
       </c>
       <c r="G14" s="163">
         <v>10</v>
@@ -36835,19 +36906,19 @@
       <c r="AC14" s="157"/>
       <c r="AD14" s="157"/>
       <c r="AE14" s="164" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AF14" s="165" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AG14" s="166" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH14" s="167" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AI14" s="86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
   </sheetData>
